--- a/src/attributions/attributions_saliency_traj_331.xlsx
+++ b/src/attributions/attributions_saliency_traj_331.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1218369454145432</v>
+        <v>0.002755129477009177</v>
       </c>
       <c r="B3" t="n">
-        <v>1.128921151161194</v>
+        <v>0.002742305630818009</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1170903667807579</v>
+        <v>6.763625424355268e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.241799458861351</v>
+        <v>0.0006568637909367681</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2542877495288849</v>
+        <v>0.0006122401100583375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08236409723758698</v>
+        <v>0.001580969663336873</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0540260374546051</v>
+        <v>0.001481498824432492</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03084775619208813</v>
+        <v>7.181684486567974e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06695470213890076</v>
+        <v>0.0009882492013275623</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2257925719022751</v>
+        <v>0.002173268934711814</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9564793109893799</v>
+        <v>0.005204176995903254</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05006644502282143</v>
+        <v>0.0002784098032861948</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4547253549098969</v>
+        <v>0.002245869487524033</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3488337695598602</v>
+        <v>0.0003140346379950643</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08225761353969574</v>
+        <v>0.001981138484552503</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08110616356134415</v>
+        <v>0.0008908662712201476</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1148066073656082</v>
+        <v>0.002422763034701347</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1703599691390991</v>
+        <v>0.0004234474909026176</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04744552448391914</v>
+        <v>0.0003639831847976893</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2470319420099258</v>
+        <v>0.0005268153036013246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05438258498907089</v>
+        <v>0.0004423994687385857</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0577487125992775</v>
+        <v>0.000520066823810339</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2032551318407059</v>
+        <v>0.0003248571010772139</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09192245453596115</v>
+        <v>4.626143709174357e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01193566806614399</v>
+        <v>0.0001780443853931502</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.102772131562233</v>
+        <v>0.0005450001917779446</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02540982887148857</v>
+        <v>0.0005861685494892299</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1207468509674072</v>
+        <v>0.0003233369789086282</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1702865064144135</v>
+        <v>6.06905814493075e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1230636388063431</v>
+        <v>0.0005961668794043362</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1031090170145035</v>
+        <v>0.00140205433126539</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1558815985918045</v>
+        <v>0.0003116929729003459</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1492897570133209</v>
+        <v>0.0003951565886382014</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02195443399250507</v>
+        <v>0.0003708109143190086</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.01710829883813858</v>
+        <v>0.001135315047577024</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.03708501532673836</v>
+        <v>4.651311610359699e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1283907145261765</v>
+        <v>0.0002801145892590284</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.111383818089962</v>
+        <v>0.0009738171356730163</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0018715166952461</v>
+        <v>0.0004495478351600468</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.08689481019973755</v>
+        <v>9.697652421891689e-05</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.06210555881261826</v>
+        <v>0.001168317394331098</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1678070425987244</v>
+        <v>0.0004961915547028184</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.01807139813899994</v>
+        <v>0.0002855748753063381</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.02459454536437988</v>
+        <v>0.001242321217432618</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.01708030514419079</v>
+        <v>1.266053004655987e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.004501345101743937</v>
+        <v>0.000532295904122293</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.6430382132530212</v>
+        <v>0.003547854255884886</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1153908893465996</v>
+        <v>0.0003495871787890792</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1961202770471573</v>
+        <v>0.002125610830262303</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1712572425603867</v>
+        <v>0.000800719135440886</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.06302840262651443</v>
+        <v>0.0007518122438341379</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2042251527309418</v>
+        <v>0.0001216468663187698</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.05289780348539352</v>
+        <v>0.0001735762052703649</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.03098005801439285</v>
+        <v>0.000339118589181453</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.03820206969976425</v>
+        <v>0.001614328939467669</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.2047334909439087</v>
+        <v>0.001071534585207701</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1279834359884262</v>
+        <v>0.0004710933717433363</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1658279001712799</v>
+        <v>0.0006997875170782208</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.2444874346256256</v>
+        <v>0.000775319233071059</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.05786384269595146</v>
+        <v>0.0006234210450202227</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.05213800817728043</v>
+        <v>4.032472497783601e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.02413827180862427</v>
+        <v>0.0001609244500286877</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1053547337651253</v>
+        <v>0.00138748437166214</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0449892170727253</v>
+        <v>0.000359922501957044</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03430169820785522</v>
+        <v>0.0005542720318771899</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.02380029112100601</v>
+        <v>0.0003319411189295352</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.08296403288841248</v>
+        <v>0.0003909789957106113</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2386744171380997</v>
+        <v>0.000403886690037325</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.126008078455925</v>
+        <v>0.0003257105709053576</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.09021922200918198</v>
+        <v>0.001554661081172526</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.09510066360235214</v>
+        <v>0.0003324613790027797</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.11845862865448</v>
+        <v>2.848210351658054e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.03798168525099754</v>
+        <v>9.392279025632888e-06</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.358279675245285</v>
+        <v>0.002592399250715971</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.130535215139389</v>
+        <v>0.0005475560901686549</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.02653029002249241</v>
+        <v>0.001851986278779805</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1187946572899818</v>
+        <v>0.0005778188933618367</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.003736862912774086</v>
+        <v>0.000446314545115456</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.07981708645820618</v>
+        <v>0.000799922680016607</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0378437228500843</v>
+        <v>0.0002093473449349403</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.03105015307664871</v>
+        <v>0.0004744734324049205</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.008083472028374672</v>
+        <v>0.000336131954099983</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.211746871471405</v>
+        <v>0.001161067513749003</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.01177240163087845</v>
+        <v>0.0001989718584809452</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.001974299550056458</v>
+        <v>0.0001819378230720758</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.003859755117446184</v>
+        <v>0.0004727211780846119</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.03741331398487091</v>
+        <v>0.0001149030067608692</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.02475113235414028</v>
+        <v>0.000227568598347716</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.02310529351234436</v>
+        <v>1.956454616447445e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.04136035963892937</v>
+        <v>0.0003881720185745507</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.213249459862709</v>
+        <v>0.0007580331875942647</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.08739730715751648</v>
+        <v>0.002414312213659286</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0712021216750145</v>
+        <v>0.0004439408658072352</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1912979334592819</v>
+        <v>0.002355188364163041</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.2832147777080536</v>
+        <v>0.0009781531989574432</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1403789073228836</v>
+        <v>9.574290015734732e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.09774154424667358</v>
+        <v>0.0007700410205870867</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1511623859405518</v>
+        <v>0.0002562698791734874</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.07997986674308777</v>
+        <v>0.0008428500150330365</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.006630952470004559</v>
+        <v>6.289856537478045e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2140029966831207</v>
+        <v>0.001187077607028186</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.03630870208144188</v>
+        <v>8.177565177902579e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.04044207558035851</v>
+        <v>0.0004246737225912511</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.002174268942326307</v>
+        <v>0.0009151312988251448</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01439603045582771</v>
+        <v>9.980921458918601e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.05782684683799744</v>
+        <v>0.0001132719771703705</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.03504250943660736</v>
+        <v>9.990216494770721e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.03203003853559494</v>
+        <v>0.0004748089122585952</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09826729446649551</v>
+        <v>4.042805812787265e-06</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.4026438295841217</v>
+        <v>0.002951486501842737</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.09945405274629593</v>
+        <v>0.000350368267390877</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.004629375413060188</v>
+        <v>0.0001267525367438793</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.05631740391254425</v>
+        <v>0.000213641847949475</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.03896027058362961</v>
+        <v>0.001025712699629366</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.01680844835937023</v>
+        <v>0.0003785337321460247</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.04557407647371292</v>
+        <v>0.001302734133787453</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.01214445941150188</v>
+        <v>0.0006548895034939051</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.06854121387004852</v>
+        <v>0.000110800625407137</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.1468450427055359</v>
+        <v>0.000193683838006109</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.05742880329489708</v>
+        <v>4.594762140186504e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1332299411296844</v>
+        <v>0.0006359597900882363</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1210971176624298</v>
+        <v>0.0008846941054798663</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.005699343979358673</v>
+        <v>0.0002532474463805556</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.04609908908605576</v>
+        <v>0.0003318701346870512</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.04782704263925552</v>
+        <v>0.0005925507284700871</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.01045194081962109</v>
+        <v>0.0008351745782420039</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0171554908156395</v>
+        <v>0.0005629416555166245</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2594024240970612</v>
+        <v>0.001622811192646623</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.04827121645212173</v>
+        <v>0.0006667093839496374</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.1138868555426598</v>
+        <v>0.0008128092740662396</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.04183195158839226</v>
+        <v>4.265145980753005e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.1265327483415604</v>
+        <v>0.0005898602539673448</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.008498549461364746</v>
+        <v>0.0005911275511607528</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.1655428558588028</v>
+        <v>0.0007982415263541043</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.06000705808401108</v>
+        <v>0.001404185662977397</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.01029099710285664</v>
+        <v>4.180765245109797e-06</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.09289843589067459</v>
+        <v>1.429140684194863e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.01345679257065058</v>
+        <v>0.0001101332818507217</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.02331589348614216</v>
+        <v>4.163396079093218e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.07621035724878311</v>
+        <v>0.0007523475214838982</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.02582333981990814</v>
+        <v>1.799654273781925e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.09610112011432648</v>
+        <v>7.669721526326612e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0233546756207943</v>
+        <v>0.0002765565295703709</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.05291507765650749</v>
+        <v>0.0002707112871576101</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.003254950046539307</v>
+        <v>6.680354999843985e-05</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1760057806968689</v>
+        <v>0.0008333902223967016</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.1000989302992821</v>
+        <v>0.0004597601655405015</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.04856729507446289</v>
+        <v>0.0001986268034670502</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03897129371762276</v>
+        <v>0.0001200592232635245</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0002361955121159554</v>
+        <v>0.00108585215639323</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.01840178854763508</v>
+        <v>0.0004105595871806145</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.003256155643612146</v>
+        <v>0.0003959887544624507</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.02921904250979424</v>
+        <v>0.0004412534763105214</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.03305087238550186</v>
+        <v>0.0001563994155731052</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2301012426614761</v>
+        <v>0.001618735608644783</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.005989811383187771</v>
+        <v>8.973678632173687e-06</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.005298951640725136</v>
+        <v>0.0003907648497261107</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01114368159323931</v>
+        <v>0.0008360490901395679</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.002950234804302454</v>
+        <v>3.13822238240391e-06</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.05469157174229622</v>
+        <v>0.0002275218575960025</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.04519356787204742</v>
+        <v>4.899982013739645e-05</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.02336808107793331</v>
+        <v>0.0004880875931121409</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01623372547328472</v>
+        <v>0.000148054605233483</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.05879342555999756</v>
+        <v>0.0007896437309682369</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.02700737118721008</v>
+        <v>0.0005294137517921627</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.02539943903684616</v>
+        <v>0.0007574973278678954</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1210647001862526</v>
+        <v>0.0004690037458203733</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.04125760123133659</v>
+        <v>0.001013741130009294</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.07490599155426025</v>
+        <v>2.032263364526443e-05</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.03195472061634064</v>
+        <v>0.0007706822943873703</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.005456605926156044</v>
+        <v>0.0003555145522113889</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06360703706741333</v>
+        <v>0.001018021255731583</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1698195934295654</v>
+        <v>0.0001572635082993656</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.07764798402786255</v>
+        <v>0.0002522125141695142</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.07480640709400177</v>
+        <v>0.001050418009981513</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04517130181193352</v>
+        <v>0.001741137122735381</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.08594115078449249</v>
+        <v>0.0003216546028852463</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.04082638397812843</v>
+        <v>0.0005298681207932532</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2972059547901154</v>
+        <v>1.33135308715282e-05</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.04170712828636169</v>
+        <v>0.0004486830439418554</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.1157793700695038</v>
+        <v>0.000818259606603533</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.05087712407112122</v>
+        <v>0.0004837422457057983</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.01581372320652008</v>
+        <v>9.267983841709793e-05</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.0992763340473175</v>
+        <v>0.000156593625433743</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.324241042137146</v>
+        <v>0.001705701346509159</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1712769567966461</v>
+        <v>0.0003012812230736017</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.1065809801220894</v>
+        <v>0.001187378074973822</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.1239957436919212</v>
+        <v>0.0002011321194004267</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.01188496965914965</v>
+        <v>5.841295205755159e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2706,5123 +2706,5123 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0001441172207705677</v>
+        <v>0.0249809417873621</v>
       </c>
       <c r="B5" t="n">
-        <v>0.002425110200420022</v>
+        <v>0.1321636140346527</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000146242295159027</v>
+        <v>0.02230219915509224</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001083231763914227</v>
+        <v>0.100540429353714</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000512606929987669</v>
+        <v>0.06894337385892868</v>
       </c>
       <c r="F5" t="n">
-        <v>3.814393494394608e-06</v>
+        <v>0.05699346214532852</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002830433659255505</v>
+        <v>0.0372479036450386</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004842132912017405</v>
+        <v>0.06161563843488693</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001044922100845724</v>
+        <v>0.009338269010186195</v>
       </c>
       <c r="J5" t="n">
-        <v>2.967074397020042e-05</v>
+        <v>0.005937238223850727</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002280444372445345</v>
+        <v>0.1405194103717804</v>
       </c>
       <c r="L5" t="n">
-        <v>9.463791502639651e-05</v>
+        <v>0.00438026525080204</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001266006729565561</v>
+        <v>0.140597939491272</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0002895482466556132</v>
+        <v>0.0917731449007988</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003589920816011727</v>
+        <v>0.05950625985860825</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002315669698873535</v>
+        <v>0.050798200070858</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001569878513691947</v>
+        <v>0.01130071096122265</v>
       </c>
       <c r="R5" t="n">
-        <v>3.101848778896965e-05</v>
+        <v>0.01487151812762022</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001356453140033409</v>
+        <v>0.009743491187691689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0004705135361291468</v>
+        <v>0.01255329046398401</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0002925860753748566</v>
+        <v>0.008893637917935848</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001373452541884035</v>
+        <v>0.004939313046634197</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0004749154904857278</v>
+        <v>0.02196676470339298</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0005062376148998737</v>
+        <v>0.02481687813997269</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003043961769435555</v>
+        <v>0.004039105959236622</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.081693234387785e-05</v>
+        <v>0.01898285374045372</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001730312069412321</v>
+        <v>0.0122379632666707</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001152868499048054</v>
+        <v>0.003075134009122849</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0007927693659439683</v>
+        <v>0.01416386850178242</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.236808308633044e-06</v>
+        <v>0.0005101985298097134</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0003952598781324923</v>
+        <v>0.02528052031993866</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0001013938672258519</v>
+        <v>0.00015019450802356</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0003409287892282009</v>
+        <v>0.006067863665521145</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0004948889836668968</v>
+        <v>0.0002971133217215538</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0004091660957783461</v>
+        <v>0.03794826194643974</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0002459214592818171</v>
+        <v>0.001029594335705042</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0001484512467868626</v>
+        <v>0.001348221674561501</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.295619899290614e-05</v>
+        <v>0.03256488591432571</v>
       </c>
       <c r="AM5" t="n">
-        <v>9.363654680782929e-05</v>
+        <v>0.004770622588694096</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0004548606812022626</v>
+        <v>0.01882139220833778</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0002264780923724174</v>
+        <v>0.00347418780438602</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0001705901813693345</v>
+        <v>0.01348876394331455</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0002051570918411016</v>
+        <v>0.007952288724482059</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0001854083384387195</v>
+        <v>0.02009820379316807</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.007072756299749e-05</v>
+        <v>0.01078489422798157</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.083772521174978e-06</v>
+        <v>0.01063289493322372</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001243641367182136</v>
+        <v>0.1166250482201576</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0004396052099764347</v>
+        <v>0.0184248723089695</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.000452801090432331</v>
+        <v>0.06645959615707397</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001073892810381949</v>
+        <v>0.07470007240772247</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0003192453878000379</v>
+        <v>0.0240924060344696</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0002275521837873384</v>
+        <v>0.005172467324882746</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0006884152535349131</v>
+        <v>4.82252798974514e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0002751263964455575</v>
+        <v>0.0143031207844615</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0003562405763659626</v>
+        <v>0.03422786667943001</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0004841448972001672</v>
+        <v>0.02652836591005325</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0005751259159296751</v>
+        <v>0.01114093791693449</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.360266757430509e-05</v>
+        <v>0.0003904575132764876</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0004763930919580162</v>
+        <v>0.006237388588488102</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.614810940343887e-05</v>
+        <v>0.02462155371904373</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0001182461273856461</v>
+        <v>0.01240865141153336</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0001901220675790682</v>
+        <v>0.03147317841649055</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0002421294630039483</v>
+        <v>0.00367225962691009</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0002995239337906241</v>
+        <v>0.008193029090762138</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0001937307824846357</v>
+        <v>0.03022146597504616</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.427271101623774e-05</v>
+        <v>9.840291022555903e-05</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0007003892678767443</v>
+        <v>0.003275064751505852</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0006358076352626085</v>
+        <v>0.0226414930075407</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.000362191058229655</v>
+        <v>0.003963382914662361</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0001621466944925487</v>
+        <v>0.03739739954471588</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.401835758471861e-05</v>
+        <v>0.01502731721848249</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.000485223950818181</v>
+        <v>0.008108831942081451</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.367328751366585e-06</v>
+        <v>0.01494028884917498</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0007967482670210302</v>
+        <v>0.08118351548910141</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.663391054142267e-05</v>
+        <v>0.003328688675537705</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.2389991247328e-05</v>
+        <v>0.05477402359247208</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.00054146972252056</v>
+        <v>0.03798430413007736</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0001056911642081104</v>
+        <v>0.02691259048879147</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0003039086877834052</v>
+        <v>0.01670500077307224</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0002467675949446857</v>
+        <v>0.01254320982843637</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.000121141696581617</v>
+        <v>0.003223436884582043</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.661842078552581e-05</v>
+        <v>0.0003901957534253597</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0004971688613295555</v>
+        <v>0.03898391127586365</v>
       </c>
       <c r="CF5" t="n">
-        <v>1.685690403974149e-05</v>
+        <v>0.004429368302226067</v>
       </c>
       <c r="CG5" t="n">
-        <v>8.339254418388009e-05</v>
+        <v>0.02997970208525658</v>
       </c>
       <c r="CH5" t="n">
-        <v>7.805328641552478e-05</v>
+        <v>0.01362620759755373</v>
       </c>
       <c r="CI5" t="n">
-        <v>3.002129778906237e-05</v>
+        <v>0.005853981710970402</v>
       </c>
       <c r="CJ5" t="n">
-        <v>8.737886673770845e-05</v>
+        <v>0.01210257038474083</v>
       </c>
       <c r="CK5" t="n">
-        <v>3.845391984214075e-05</v>
+        <v>0.005908326245844364</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.458742710587103e-05</v>
+        <v>0.003705517621710896</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0004936330369673669</v>
+        <v>0.01164573989808559</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0001924645039252937</v>
+        <v>0.09422710537910461</v>
       </c>
       <c r="CO5" t="n">
-        <v>9.484363545197994e-06</v>
+        <v>0.03468082845211029</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0007266509346663952</v>
+        <v>0.05885839462280273</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0004376550787128508</v>
+        <v>0.001726731657981873</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0007428863900713623</v>
+        <v>0.004268573131412268</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0001714989048196003</v>
+        <v>0.01411031559109688</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0001078323912224732</v>
+        <v>0.01434663683176041</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0001346627250313759</v>
+        <v>0.001111395657062531</v>
       </c>
       <c r="CV5" t="n">
-        <v>6.941385800018907e-05</v>
+        <v>0.003942528739571571</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0004715010290965438</v>
+        <v>0.03763546794652939</v>
       </c>
       <c r="CX5" t="n">
-        <v>9.766890434548259e-05</v>
+        <v>0.00348458020016551</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0002178719878429547</v>
+        <v>0.03766889870166779</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001645422162255272</v>
+        <v>0.006843827664852142</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.107234649884049e-06</v>
+        <v>0.00434016901999712</v>
       </c>
       <c r="DB5" t="n">
-        <v>9.973185660783201e-05</v>
+        <v>0.01027398835867643</v>
       </c>
       <c r="DC5" t="n">
-        <v>4.310192889533937e-05</v>
+        <v>0.003554003313183784</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.428263516980223e-05</v>
+        <v>0.005215417593717575</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0002551644283812493</v>
+        <v>0.02722209319472313</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0003344675642438233</v>
+        <v>0.05544617772102356</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0002325983950868249</v>
+        <v>0.01891661249101162</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0001794060954125598</v>
+        <v>0.03879925608634949</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0007334948168136179</v>
+        <v>0.01072917878627777</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.718276300583966e-05</v>
+        <v>0.021552799269557</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0002185825142078102</v>
+        <v>0.0001296335831284523</v>
       </c>
       <c r="DL5" t="n">
-        <v>9.063083416549489e-05</v>
+        <v>0.04423847794532776</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0002418411604594439</v>
+        <v>0.01101744547486305</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0002283445792272687</v>
+        <v>0.01801654696464539</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003486575151327997</v>
+        <v>0.01444356981664896</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0001884273660834879</v>
+        <v>0.005731532350182533</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0004416769370436668</v>
+        <v>0.001302599906921387</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0002793392341118306</v>
+        <v>0.00867621973156929</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.000139933661557734</v>
+        <v>0.006459961645305157</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001249568886123598</v>
+        <v>0.005914757493883371</v>
       </c>
       <c r="DU5" t="n">
-        <v>8.639198313176166e-06</v>
+        <v>0.02536690793931484</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0004204384167678654</v>
+        <v>0.03509948030114174</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0001628378231544048</v>
+        <v>0.01712510734796524</v>
       </c>
       <c r="DX5" t="n">
-        <v>7.392106635961682e-05</v>
+        <v>6.619701161980629e-05</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.148771793348715e-05</v>
+        <v>0.006434498820453882</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0001549035951029509</v>
+        <v>0.03707955777645111</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.676127769518644e-05</v>
+        <v>0.007368593476712704</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0001376292348140851</v>
+        <v>0.009315001778304577</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0001049836864694953</v>
+        <v>0.003089099191129208</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0004068278940394521</v>
+        <v>0.04065465927124023</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0002376280317548662</v>
+        <v>0.02312596328556538</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0002960908750537783</v>
+        <v>0.02518232353031635</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0002800269867293537</v>
+        <v>0.02255285158753395</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0002030842879321426</v>
+        <v>0.0007873382419347763</v>
       </c>
       <c r="EI5" t="n">
-        <v>5.704363866243511e-05</v>
+        <v>0.02409650385379791</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0002683698257897049</v>
+        <v>0.004614416509866714</v>
       </c>
       <c r="EK5" t="n">
-        <v>4.218096728436649e-05</v>
+        <v>0.009289282374083996</v>
       </c>
       <c r="EL5" t="n">
-        <v>8.462193363811821e-05</v>
+        <v>0.007212919183075428</v>
       </c>
       <c r="EM5" t="n">
-        <v>8.550527854822576e-05</v>
+        <v>0.005276553798466921</v>
       </c>
       <c r="EN5" t="n">
-        <v>7.456580351572484e-05</v>
+        <v>0.001666786032728851</v>
       </c>
       <c r="EO5" t="n">
-        <v>4.22077500843443e-05</v>
+        <v>0.005613356828689575</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0004536989727057517</v>
+        <v>0.03505030274391174</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.00018080766312778</v>
+        <v>0.01481959037482738</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0006324058631435037</v>
+        <v>0.006370702758431435</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0003689859586302191</v>
+        <v>0.006296169478446245</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.000111194429337047</v>
+        <v>0.0002719134790822864</v>
       </c>
       <c r="EU5" t="n">
-        <v>9.728872828418389e-05</v>
+        <v>0.02003257349133492</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0003472967073321342</v>
+        <v>0.01363433338701725</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001470458082621917</v>
+        <v>0.02420702017843723</v>
       </c>
       <c r="EX5" t="n">
-        <v>1.240363417309709e-05</v>
+        <v>0.002405597828328609</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0005246951477602124</v>
+        <v>0.04605470597743988</v>
       </c>
       <c r="EZ5" t="n">
-        <v>1.34546007757308e-05</v>
+        <v>0.0008298968896269798</v>
       </c>
       <c r="FA5" t="n">
-        <v>7.59476752136834e-05</v>
+        <v>0.03891774266958237</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0001548272557556629</v>
+        <v>0.006248426157981157</v>
       </c>
       <c r="FC5" t="n">
-        <v>9.881008008960634e-05</v>
+        <v>0.005758365150541067</v>
       </c>
       <c r="FD5" t="n">
-        <v>6.447541090892628e-05</v>
+        <v>0.01362805813550949</v>
       </c>
       <c r="FE5" t="n">
-        <v>3.988101525465026e-05</v>
+        <v>0.01304446067661047</v>
       </c>
       <c r="FF5" t="n">
-        <v>7.553567411378026e-05</v>
+        <v>0.005771113093942404</v>
       </c>
       <c r="FG5" t="n">
-        <v>1.660201087361202e-05</v>
+        <v>0.01711664721369743</v>
       </c>
       <c r="FH5" t="n">
-        <v>1.836210140027106e-05</v>
+        <v>0.02692059986293316</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.000317575060762465</v>
+        <v>0.009095650166273117</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0002178957947762683</v>
+        <v>0.03356616199016571</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0002777610206976533</v>
+        <v>0.00879782997071743</v>
       </c>
       <c r="FL5" t="n">
-        <v>8.76295889611356e-05</v>
+        <v>0.002415852155536413</v>
       </c>
       <c r="FM5" t="n">
-        <v>4.817023000214249e-05</v>
+        <v>0.00726409675553441</v>
       </c>
       <c r="FN5" t="n">
-        <v>6.649395800195634e-05</v>
+        <v>0.001886451500467956</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0003184436936862767</v>
+        <v>0.0100703788921237</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0003147159295622259</v>
+        <v>0.01856051199138165</v>
       </c>
       <c r="FQ5" t="n">
-        <v>5.035134381614625e-05</v>
+        <v>0.04268521070480347</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0005863024853169918</v>
+        <v>0.0288423839956522</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0003777598612941802</v>
+        <v>0.05510315671563148</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0001330862141912803</v>
+        <v>0.1022162586450577</v>
       </c>
       <c r="FU5" t="n">
-        <v>8.512180647812784e-05</v>
+        <v>0.02461353316903114</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0004757724236696959</v>
+        <v>0.005867521278560162</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0004921971121802926</v>
+        <v>0.0007303422316908836</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0003624140226747841</v>
+        <v>0.04027926921844482</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0002417685609543696</v>
+        <v>0.01255171187222004</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0001101537491194904</v>
+        <v>0.002774457447230816</v>
       </c>
       <c r="GA5" t="n">
-        <v>1.99343339772895e-05</v>
+        <v>0.00673727598041296</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0001660812995396554</v>
+        <v>0.003215665929019451</v>
       </c>
       <c r="GC5" t="n">
-        <v>5.93497788941022e-05</v>
+        <v>0.02270718477666378</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0005043686251156032</v>
+        <v>0.01112229842692614</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0007429180550388992</v>
+        <v>0.02864423021674156</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.999344385694712e-05</v>
+        <v>0.01772512681782246</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0002858702500816435</v>
+        <v>0.001700390363112092</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.05469995737075806</v>
+        <v>2.592736564110965e-06</v>
       </c>
       <c r="B6" t="n">
-        <v>0.08678995817899704</v>
+        <v>1.308456558035687e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01071652118116617</v>
+        <v>3.514376885505044e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001519256038591266</v>
+        <v>1.804908151825657e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0645187720656395</v>
+        <v>5.033833986090031e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01842094212770462</v>
+        <v>3.468082240942749e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02682918682694435</v>
+        <v>3.883322960973601e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02481719478964806</v>
+        <v>2.195476582755873e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002533722203224897</v>
+        <v>1.223427602781157e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0313534289598465</v>
+        <v>5.875788815501437e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>0.09011940658092499</v>
+        <v>1.691042052698322e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007225492037832737</v>
+        <v>3.248513394282782e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03980639576911926</v>
+        <v>3.509553380354191e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07871870696544647</v>
+        <v>7.251186616485938e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02907432243227959</v>
+        <v>1.566962964716367e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0347345769405365</v>
+        <v>1.999159849219723e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0439826175570488</v>
+        <v>2.222510829597013e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01196738705039024</v>
+        <v>1.856715243775398e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001133705372922122</v>
+        <v>3.140683304536651e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04084353148937225</v>
+        <v>2.176420366595266e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01175261847674847</v>
+        <v>3.393451493138855e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03710087388753891</v>
+        <v>1.399624807163491e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03004567883908749</v>
+        <v>1.658901567225257e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02893455140292645</v>
+        <v>1.105268694345796e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02683764882385731</v>
+        <v>4.82389509670611e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001493360847234726</v>
+        <v>1.556766505927953e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003745324444025755</v>
+        <v>1.095580614673963e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03525113686919212</v>
+        <v>3.2875007605071e-08</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.04516131803393364</v>
+        <v>3.337019620630599e-07</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01005097944289446</v>
+        <v>2.396270247118082e-06</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.004059469792991877</v>
+        <v>1.582108552611317e-06</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02459194324910641</v>
+        <v>3.353984538989607e-07</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001994753256440163</v>
+        <v>5.64873573694058e-07</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.04374672472476959</v>
+        <v>8.909451025829185e-07</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.003758816746994853</v>
+        <v>2.813896571751684e-06</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.005373968277126551</v>
+        <v>1.711675395199563e-06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.007207692600786686</v>
+        <v>2.960486256142758e-07</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02880655787885189</v>
+        <v>4.374121999717318e-06</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001433071796782315</v>
+        <v>6.377825911840773e-08</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.001590246800333261</v>
+        <v>6.649569854744186e-07</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.01731070317327976</v>
+        <v>2.870760681616957e-06</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.009773524478077888</v>
+        <v>1.467080323891423e-06</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.001372488331981003</v>
+        <v>9.024795417644782e-07</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003966072574257851</v>
+        <v>1.522166940048919e-06</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.01438361592590809</v>
+        <v>2.832688608123135e-07</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.008195248432457447</v>
+        <v>9.357995054415369e-07</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05442678928375244</v>
+        <v>1.181587140308693e-05</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.005597800016403198</v>
+        <v>1.656348558753962e-06</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.001063545234501362</v>
+        <v>5.365802735468606e-07</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0001727864146232605</v>
+        <v>2.00409840545035e-06</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.01890461705625057</v>
+        <v>1.094574599846965e-06</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.01420655287802219</v>
+        <v>6.010565130054601e-07</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.01700520887970924</v>
+        <v>1.051831304721418e-06</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.003793076612055302</v>
+        <v>7.433683890667453e-08</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.004830517806112766</v>
+        <v>2.436358954582829e-06</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01215296983718872</v>
+        <v>1.524171352684789e-06</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.004265547730028629</v>
+        <v>4.009501026303042e-06</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.007919834926724434</v>
+        <v>4.842090675083455e-07</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.07044529914855957</v>
+        <v>2.775826715151197e-06</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001136911567300558</v>
+        <v>1.191506612485682e-06</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.03073825128376484</v>
+        <v>7.147285145947535e-07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.003841795958578587</v>
+        <v>1.845788233367784e-07</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.002661853563040495</v>
+        <v>1.653084069630495e-07</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.01344913430511951</v>
+        <v>8.458894171781139e-07</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04179380089044571</v>
+        <v>1.114364749810193e-06</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.01723324693739414</v>
+        <v>6.110401500336593e-07</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.002921209437772632</v>
+        <v>3.180052488005458e-07</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02094918303191662</v>
+        <v>1.725252900541818e-06</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01444033440202475</v>
+        <v>3.637355519003904e-07</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.007829471491277218</v>
+        <v>1.708150648482842e-06</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01778808608651161</v>
+        <v>1.5174185818978e-07</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.01025431975722313</v>
+        <v>6.96202903327503e-07</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.005798950791358948</v>
+        <v>6.268664947128855e-07</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0477653332054615</v>
+        <v>9.31735758058494e-06</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.01240878645330667</v>
+        <v>2.738901514476311e-07</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.004898312501609325</v>
+        <v>1.798399921426608e-06</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0002050078473985195</v>
+        <v>8.74708860010287e-07</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.003596951486542821</v>
+        <v>1.684971266513458e-06</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0009696629131212831</v>
+        <v>1.061874627339421e-06</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.01940140128135681</v>
+        <v>1.412804380152011e-07</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.002996726427227259</v>
+        <v>1.366890955978306e-06</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.00776847917586565</v>
+        <v>3.098543857049663e-07</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.02008460648357868</v>
+        <v>4.478381924855057e-06</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.001233580056577921</v>
+        <v>9.107907317229547e-07</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.004688397515565157</v>
+        <v>3.983965086717944e-07</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002903773449361324</v>
+        <v>6.677952342215576e-07</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.003684157505631447</v>
+        <v>1.233982175108395e-06</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0104431938380003</v>
+        <v>6.857153778128122e-08</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.004870246164500713</v>
+        <v>6.663573230980546e-07</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0003547169035300612</v>
+        <v>5.347474143491127e-07</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.03146318718791008</v>
+        <v>5.07234631186293e-07</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.007104784250259399</v>
+        <v>7.152388661779696e-06</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0003613968729041517</v>
+        <v>1.419238174094062e-06</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0008491412736475468</v>
+        <v>2.514771608730371e-07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.004562105052173138</v>
+        <v>3.099065679634805e-07</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.01149975229054689</v>
+        <v>5.461106979964825e-07</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.01038704067468643</v>
+        <v>6.679389343844377e-07</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.01588146947324276</v>
+        <v>1.778140244823589e-06</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.006077012047171593</v>
+        <v>2.077956366974831e-07</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.007361066527664661</v>
+        <v>2.616705216951232e-07</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0236828476190567</v>
+        <v>4.555626219371334e-06</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.003578101051971316</v>
+        <v>8.585517434767098e-07</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.00554811954498291</v>
+        <v>2.471876427989628e-07</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.278030246496201e-05</v>
+        <v>3.689838763420994e-07</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.007391813211143017</v>
+        <v>1.093850983124867e-06</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.009159257635474205</v>
+        <v>2.488308155079721e-07</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.01030428521335125</v>
+        <v>7.886278581281658e-07</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.003503241576254368</v>
+        <v>1.019845399241603e-06</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.01792536117136478</v>
+        <v>1.089442207558022e-06</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.008463518694043159</v>
+        <v>4.970100690115942e-06</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.002402150770649314</v>
+        <v>3.453709496170632e-08</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.05851951614022255</v>
+        <v>5.848525574947416e-07</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0187162384390831</v>
+        <v>6.230812914509443e-07</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0022280253469944</v>
+        <v>2.931006520157098e-06</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.006040375214070082</v>
+        <v>2.394048124187975e-07</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.01212923787534237</v>
+        <v>1.139005348704814e-06</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.02005673758685589</v>
+        <v>6.924086051185441e-07</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.006142071448266506</v>
+        <v>4.581106054502015e-07</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01472907699644566</v>
+        <v>2.655804109963356e-06</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01313267648220062</v>
+        <v>1.001370719677652e-07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.01907916367053986</v>
+        <v>2.590834640159301e-07</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01085632760077715</v>
+        <v>1.706216181673881e-07</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.02469468675553799</v>
+        <v>2.594585737369925e-07</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.02365382015705109</v>
+        <v>2.234025373581972e-07</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.00177352677565068</v>
+        <v>1.929205382111832e-06</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.001162395579740405</v>
+        <v>1.614626853552181e-06</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.005617850460112095</v>
+        <v>1.593467345628596e-06</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0122163537889719</v>
+        <v>3.292526344012003e-06</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.01667114160954952</v>
+        <v>5.955719473149657e-09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.005576029885560274</v>
+        <v>1.916019698455784e-07</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01727661490440369</v>
+        <v>7.61403043725295e-07</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.01296310313045979</v>
+        <v>3.82290500056115e-06</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.001671258825808764</v>
+        <v>4.514854481385555e-07</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0235319510102272</v>
+        <v>9.626787687011529e-07</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0047487523406744</v>
+        <v>1.878489911177894e-06</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.01175815146416426</v>
+        <v>1.094613935492816e-06</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.003098106943070889</v>
+        <v>2.37379026657436e-06</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.003592245280742645</v>
+        <v>4.326950602262514e-07</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.01474251877516508</v>
+        <v>9.582015536580002e-07</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.003316012676805258</v>
+        <v>7.619019015692174e-07</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0007121668895706534</v>
+        <v>1.398099698235455e-06</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.007373490370810032</v>
+        <v>9.741341955304961e-08</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.00827132910490036</v>
+        <v>7.128737706807442e-07</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.007311772555112839</v>
+        <v>4.108890152565436e-07</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.006426974665373564</v>
+        <v>5.382391350394755e-07</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.02994275279343128</v>
+        <v>2.632924861245556e-06</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.007521621882915497</v>
+        <v>6.402390226867283e-07</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.005883709527552128</v>
+        <v>1.96083931314206e-07</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01719224639236927</v>
+        <v>2.826725520321816e-08</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.01013129204511642</v>
+        <v>2.603277096113743e-07</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.005901893600821495</v>
+        <v>2.031502503996307e-07</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.008388763293623924</v>
+        <v>2.233815621366375e-07</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0008779935305938125</v>
+        <v>7.338466616602091e-07</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.005260278936475515</v>
+        <v>2.440221464894421e-07</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.02408028766512871</v>
+        <v>5.031219188822433e-06</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.005513099487870932</v>
+        <v>8.879389383764646e-07</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.003531388938426971</v>
+        <v>2.347314307371562e-07</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.006255540996789932</v>
+        <v>2.828413698807708e-07</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.004948730580508709</v>
+        <v>1.080598963199009e-06</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.005294500850141048</v>
+        <v>1.002804808081237e-07</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.01031455863267183</v>
+        <v>7.505465760004881e-07</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0001019896590150893</v>
+        <v>1.008166009341949e-06</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.01047351770102978</v>
+        <v>7.220967859211669e-07</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.003627012018114328</v>
+        <v>1.813251401472371e-06</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.01940137892961502</v>
+        <v>1.829514758355799e-06</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.03628749772906303</v>
+        <v>8.808415827843419e-07</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.01222977228462696</v>
+        <v>5.751816161136958e-07</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.002461973112076521</v>
+        <v>1.033121634463896e-06</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.01590890623629093</v>
+        <v>7.926287253212649e-07</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.001639113994315267</v>
+        <v>6.867784350106376e-07</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.01413817051798105</v>
+        <v>2.022723947447957e-06</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.01790762692689896</v>
+        <v>3.579929853003705e-06</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.05351405218243599</v>
+        <v>2.98691566058551e-06</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.009385610930621624</v>
+        <v>2.682947524590418e-06</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.01859617792069912</v>
+        <v>2.729386324062943e-06</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.008843142539262772</v>
+        <v>2.377374812567723e-06</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.008546316996216774</v>
+        <v>5.999040126880573e-07</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.02137996070086956</v>
+        <v>1.17860906811984e-06</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.02484026551246643</v>
+        <v>2.717319830480847e-06</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.002135558053851128</v>
+        <v>3.508348754621693e-06</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.02236267738044262</v>
+        <v>8.337952976944507e-07</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.005701504182070494</v>
+        <v>2.810989144563791e-06</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.009755668230354786</v>
+        <v>1.185325459118758e-06</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0002283863723278046</v>
+        <v>2.300797063981008e-07</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0436347983777523</v>
+        <v>8.183939712580468e-07</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.004308484029024839</v>
+        <v>5.517154590961582e-07</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.04264188557863235</v>
+        <v>7.48306661080278e-07</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.02708936855196953</v>
+        <v>4.878477852798824e-07</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.002097936347126961</v>
+        <v>1.215485099237412e-06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001654379535466433</v>
+        <v>0.04533899948000908</v>
       </c>
       <c r="B7" t="n">
-        <v>0.05990925058722496</v>
+        <v>0.7054626941680908</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004476746544241905</v>
+        <v>0.1852566599845886</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03296861425042152</v>
+        <v>0.6406623125076294</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01543734967708588</v>
+        <v>0.2913648784160614</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009506619535386562</v>
+        <v>0.126239076256752</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006374484859406948</v>
+        <v>0.193175196647644</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004016528837382793</v>
+        <v>0.1783586293458939</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003213075688108802</v>
+        <v>0.0490599162876606</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002754566958174109</v>
+        <v>0.2295078635215759</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04804715886712074</v>
+        <v>0.6042726635932922</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000586572103202343</v>
+        <v>0.1868155002593994</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03443502262234688</v>
+        <v>0.8884053230285645</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02088985219597816</v>
+        <v>0.4226991236209869</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008666696026921272</v>
+        <v>0.03118047118186951</v>
       </c>
       <c r="P7" t="n">
-        <v>0.004802749492228031</v>
+        <v>0.2027596831321716</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006059912033379078</v>
+        <v>0.03564606979489326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005282065831124783</v>
+        <v>0.05214240029454231</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00141447049099952</v>
+        <v>0.006678638979792595</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0103595582768321</v>
+        <v>0.1463361531496048</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004707092419266701</v>
+        <v>0.03737042099237442</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001929994905367494</v>
+        <v>0.0213552713394165</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004599670879542828</v>
+        <v>0.01112853549420834</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00985367875546217</v>
+        <v>0.0694139152765274</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.006699636578559875</v>
+        <v>0.0395527109503746</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001261739293113351</v>
+        <v>0.03934897482395172</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00524149788543582</v>
+        <v>0.05273877084255219</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.006448002532124519</v>
+        <v>0.04515028744935989</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.008641195483505726</v>
+        <v>0.1248920112848282</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0009418356348760426</v>
+        <v>0.02726447209715843</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002282649977132678</v>
+        <v>0.1304093599319458</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.000316668301820755</v>
+        <v>0.07051029801368713</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.003979908768087626</v>
+        <v>0.02736880630254745</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.003116640029475093</v>
+        <v>0.09266853332519531</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.001180841936729848</v>
+        <v>0.00414870772510767</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001893582753837109</v>
+        <v>0.0598439909517765</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.003837342606857419</v>
+        <v>0.008034974336624146</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.006426231004297733</v>
+        <v>0.3005483150482178</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0005995168467052281</v>
+        <v>0.01866890676319599</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001004384248517454</v>
+        <v>0.04081200435757637</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0009365705191157758</v>
+        <v>0.2988598644733429</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.004585663322359324</v>
+        <v>0.1712410748004913</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.003041692543774843</v>
+        <v>0.03165820240974426</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.005827094428241253</v>
+        <v>0.1096264719963074</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.003892227541655302</v>
+        <v>0.06246410682797432</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.002742420416325331</v>
+        <v>0.02002914994955063</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.03894216567277908</v>
+        <v>0.5420712828636169</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.003403008449822664</v>
+        <v>0.03646934032440186</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.00986798107624054</v>
+        <v>0.2842848598957062</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.00266549177467823</v>
+        <v>0.2616423368453979</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001512656570412219</v>
+        <v>0.01851396821439266</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0009813050273805857</v>
+        <v>0.04430104792118073</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.005650041624903679</v>
+        <v>0.05031949654221535</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.005460168700665236</v>
+        <v>0.1603651940822601</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.002578240586444736</v>
+        <v>0.04420535266399384</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.008677131496369839</v>
+        <v>0.09463290125131607</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01014777459204197</v>
+        <v>0.2018974274396896</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.004952566232532263</v>
+        <v>0.07087066769599915</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01649742759764194</v>
+        <v>0.06335131824016571</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.002721983473747969</v>
+        <v>0.05034919828176498</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.008706447668373585</v>
+        <v>0.02165767922997475</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.007952037267386913</v>
+        <v>0.01243738271296024</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.003379866713657975</v>
+        <v>0.1442249715328217</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.009628195315599442</v>
+        <v>0.008453547954559326</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.00251127639785409</v>
+        <v>0.1200561821460724</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001727114780806005</v>
+        <v>0.03501079976558685</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0003979401662945747</v>
+        <v>0.01839231140911579</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0008360838983207941</v>
+        <v>0.013737334869802</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.004654126241803169</v>
+        <v>0.04888087511062622</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0001645480515435338</v>
+        <v>0.02959458902478218</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.002001279732212424</v>
+        <v>0.06448274105787277</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.003842451609671116</v>
+        <v>0.07028470188379288</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.002701190067455173</v>
+        <v>0.00331787345930934</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.02177071012556553</v>
+        <v>0.457376629114151</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.003533062990754843</v>
+        <v>0.01492263004183769</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.004005481489002705</v>
+        <v>0.2324647009372711</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0008779159979894757</v>
+        <v>0.0894901305437088</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.00413363054394722</v>
+        <v>0.1498548239469528</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.001335036940872669</v>
+        <v>0.09106767177581787</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0006846684846095741</v>
+        <v>0.02424820885062218</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.004461027681827545</v>
+        <v>0.0538971871137619</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.001137042534537613</v>
+        <v>0.0024262685328722</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.009211726486682892</v>
+        <v>0.2341001629829407</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.001861920347437263</v>
+        <v>0.02273239940404892</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.005394595209509134</v>
+        <v>0.1591620743274689</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002227443968877196</v>
+        <v>0.01095653045922518</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001856132643297315</v>
+        <v>0.01223685033619404</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001722266664728522</v>
+        <v>0.007776034995913506</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0005274968571029603</v>
+        <v>0.06410057097673416</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.001142089604400098</v>
+        <v>0.04888490960001945</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.009210438467562199</v>
+        <v>0.03524849191308022</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001773547031916678</v>
+        <v>0.3690030574798584</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.00116494600661099</v>
+        <v>0.02192981541156769</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.00797044113278389</v>
+        <v>0.2046147286891937</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.007747940719127655</v>
+        <v>0.04691893607378006</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.01197742391377687</v>
+        <v>0.01832916215062141</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.005910299252718687</v>
+        <v>0.04594000428915024</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.01269947551190853</v>
+        <v>0.07621990889310837</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001662163762375712</v>
+        <v>0.01407826319336891</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0005651077954098582</v>
+        <v>0.02662737481296062</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01010839641094208</v>
+        <v>0.2467896789312363</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.003048750571906567</v>
+        <v>0.02287507802248001</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.007098172325640917</v>
+        <v>0.169850155711174</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.002122316975146532</v>
+        <v>0.03833296522498131</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.003751489333808422</v>
+        <v>0.01719462312757969</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.00164801487699151</v>
+        <v>0.01610866189002991</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0006702655809931457</v>
+        <v>0.05264515802264214</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0002946688327938318</v>
+        <v>0.04550433903932571</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0007918786141090095</v>
+        <v>0.1389815360307693</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01293616741895676</v>
+        <v>0.2928671836853027</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.00324667152017355</v>
+        <v>0.02368738502264023</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.009406132623553276</v>
+        <v>0.268385648727417</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01279637776315212</v>
+        <v>0.09939424693584442</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.005444927606731653</v>
+        <v>0.1482596397399902</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.004037292208522558</v>
+        <v>0.02812078036367893</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.004250914789736271</v>
+        <v>0.2456717044115067</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.002075540833175182</v>
+        <v>0.05529966205358505</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.001325411954894662</v>
+        <v>0.1003096848726273</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.007467271294444799</v>
+        <v>0.08600763231515884</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.005287093110382557</v>
+        <v>0.02796390652656555</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.001877925242297351</v>
+        <v>0.1397450566291809</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.005188635550439358</v>
+        <v>0.1122331470251083</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.001155511010438204</v>
+        <v>0.04410357400774956</v>
       </c>
       <c r="DT7" t="n">
-        <v>4.627558519132435e-05</v>
+        <v>0.07315219938755035</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0003616548492573202</v>
+        <v>0.01737474277615547</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.002084215637296438</v>
+        <v>0.2360725104808807</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.002719692420214415</v>
+        <v>0.004520516842603683</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.002103519160300493</v>
+        <v>0.1510384529829025</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.007681943476200104</v>
+        <v>0.0250195674598217</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.003452577162533998</v>
+        <v>0.1603112667798996</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.004321776330471039</v>
+        <v>0.0356857031583786</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.002376864431425929</v>
+        <v>0.1316708326339722</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0020978560205549</v>
+        <v>0.02711394242942333</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.00315876305103302</v>
+        <v>0.2576819062232971</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.000759661546908319</v>
+        <v>0.2186006456613541</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0008951448835432529</v>
+        <v>0.1092020496726036</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.007614592090249062</v>
+        <v>0.224754273891449</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.001245267107151449</v>
+        <v>0.04203610122203827</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.005320407915860415</v>
+        <v>0.1111195832490921</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.008165201172232628</v>
+        <v>0.07863230258226395</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.001068462617695332</v>
+        <v>0.05628082528710365</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.002687092870473862</v>
+        <v>0.01099361106753349</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0008242647745646536</v>
+        <v>0.06888091564178467</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.001763866981491446</v>
+        <v>0.006384569220244884</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.000547159812413156</v>
+        <v>0.07662983983755112</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.006484607234597206</v>
+        <v>0.2067302465438843</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.006628984585404396</v>
+        <v>0.1119333654642105</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.006748104002326727</v>
+        <v>0.1250442713499069</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.009048381820321083</v>
+        <v>0.04116984084248543</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.007874161936342716</v>
+        <v>0.1053589731454849</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.003793165553361177</v>
+        <v>0.08092715591192245</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0007472268771380186</v>
+        <v>0.03930294513702393</v>
       </c>
       <c r="EW7" t="n">
-        <v>2.137225055776071e-05</v>
+        <v>0.07342774420976639</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.000497229106258601</v>
+        <v>0.009316045790910721</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.010606424883008</v>
+        <v>0.2856014668941498</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001590294879861176</v>
+        <v>0.002713429741561413</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.006132340990006924</v>
+        <v>0.1929729878902435</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.002552476711571217</v>
+        <v>0.02840117923915386</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.003564460435882211</v>
+        <v>0.004222040064632893</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.002650092821568251</v>
+        <v>0.008820105344057083</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0008511857013218105</v>
+        <v>0.07064429670572281</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.001235588802956045</v>
+        <v>0.04791177064180374</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0006968802772462368</v>
+        <v>0.04540680348873138</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.003013442270457745</v>
+        <v>0.04797931760549545</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.001078612869605422</v>
+        <v>0.1125959157943726</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0007569173467345536</v>
+        <v>0.09073236584663391</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.001077806227840483</v>
+        <v>0.07750649750232697</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.003052516374737024</v>
+        <v>0.04221364110708237</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0009569799876771867</v>
+        <v>0.01642916537821293</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0007955817272886634</v>
+        <v>0.06047952547669411</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.00333123654127121</v>
+        <v>0.1317750066518784</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.000712865381501615</v>
+        <v>0.1232658550143242</v>
       </c>
       <c r="FQ7" t="n">
-        <v>6.726953870384023e-05</v>
+        <v>0.2969499230384827</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0013328354107216</v>
+        <v>0.1088192239403725</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.004359263926744461</v>
+        <v>0.3055122792720795</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001654643099755049</v>
+        <v>0.1339304745197296</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0001566557912155986</v>
+        <v>0.03152874112129211</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.002718937583267689</v>
+        <v>0.05432350933551788</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0004765461198985577</v>
+        <v>0.01097159273922443</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.003665935480967164</v>
+        <v>0.2226567715406418</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.005207493435591459</v>
+        <v>0.05131156742572784</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.001846368541009724</v>
+        <v>0.2064133286476135</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.002370989881455898</v>
+        <v>0.09278803318738937</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001863742247223854</v>
+        <v>0.1010162085294724</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0062620067037642</v>
+        <v>0.2263747304677963</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.003395593725144863</v>
+        <v>0.02666357532143593</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.0129069397225976</v>
+        <v>0.1677895486354828</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.002347932429984212</v>
+        <v>0.04095363616943359</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.002165518002584577</v>
+        <v>0.0903937891125679</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0009467892814427614</v>
+        <v>0.1632354259490967</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03386474773287773</v>
+        <v>0.8097057342529297</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0005235068965703249</v>
+        <v>0.01387308537960052</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01613142713904381</v>
+        <v>0.1205272823572159</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007358860224485397</v>
+        <v>0.05451839417219162</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02890066429972649</v>
+        <v>1.158368229866028</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002051356947049499</v>
+        <v>0.2069427818059921</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01161150354892015</v>
+        <v>0.4364790320396423</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001116631785407662</v>
+        <v>0.03878007829189301</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003368419129401445</v>
+        <v>0.0426887534558773</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02494616806507111</v>
+        <v>0.924742579460144</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008257883018814027</v>
+        <v>0.02924243360757828</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01954410597681999</v>
+        <v>0.06251341104507446</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009461977519094944</v>
+        <v>0.4607495963573456</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03065280988812447</v>
+        <v>0.9933497309684753</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0005235662101767957</v>
+        <v>0.04306619614362717</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.004842276684939861</v>
+        <v>0.3207272589206696</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001104073831811547</v>
+        <v>0.08232656121253967</v>
       </c>
       <c r="S8" t="n">
-        <v>0.004108157474547625</v>
+        <v>0.209868922829628</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007826001383364201</v>
+        <v>0.197099357843399</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0002947314933408052</v>
+        <v>0.3516408801078796</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003779294434934855</v>
+        <v>0.005645495373755693</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001632447238080204</v>
+        <v>0.1482521295547485</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001929801655933261</v>
+        <v>0.2325167953968048</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003806379158049822</v>
+        <v>0.2994455397129059</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002638136968016624</v>
+        <v>0.2377355545759201</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002066052053123713</v>
+        <v>0.03301514312624931</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00670121842995286</v>
+        <v>0.2728697955608368</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006620796862989664</v>
+        <v>0.2650586664676666</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0008875494240783155</v>
+        <v>0.1052560210227966</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0007338945288211107</v>
+        <v>0.4197136759757996</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.004557377658784389</v>
+        <v>0.04868130758404732</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.008722194470465183</v>
+        <v>0.125310406088829</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0032445655670017</v>
+        <v>0.1411323547363281</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.602681241929531e-05</v>
+        <v>0.343996524810791</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004332737997174263</v>
+        <v>0.2487821578979492</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0013597731012851</v>
+        <v>0.08611059188842773</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.004282827023416758</v>
+        <v>0.09081600606441498</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.001903653959743679</v>
+        <v>0.02220159024000168</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002063388470560312</v>
+        <v>0.0709688812494278</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006104969419538975</v>
+        <v>0.1116349399089813</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.007738684304058552</v>
+        <v>0.1826471984386444</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001890481100417674</v>
+        <v>0.2584970891475677</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001760246464982629</v>
+        <v>0.222240075469017</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002962854225188494</v>
+        <v>0.1267000436782837</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00286371260881424</v>
+        <v>0.1787210553884506</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0223008431494236</v>
+        <v>0.7931593656539917</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.002059363760054111</v>
+        <v>0.1719154715538025</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001476232544519007</v>
+        <v>0.08467821031808853</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0001452544238418341</v>
+        <v>0.3952804505825043</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0209322776645422</v>
+        <v>0.5530747771263123</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002181774005293846</v>
+        <v>0.2499969303607941</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00504436157643795</v>
+        <v>0.02468340843915939</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.006148883141577244</v>
+        <v>0.0582098662853241</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.004100818186998367</v>
+        <v>0.09475237876176834</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.007021388970315456</v>
+        <v>0.2243802845478058</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.006417206954210997</v>
+        <v>0.1633527278900146</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.007595024071633816</v>
+        <v>0.3837039172649384</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01197756640613079</v>
+        <v>0.1244657337665558</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.008210652507841587</v>
+        <v>0.315074622631073</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001826842897571623</v>
+        <v>0.2201485186815262</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.006539464462548494</v>
+        <v>0.3213054537773132</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.004860143177211285</v>
+        <v>0.2478149086236954</v>
       </c>
       <c r="BL8" t="n">
-        <v>9.883512393571436e-05</v>
+        <v>0.1299033463001251</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001580446027219296</v>
+        <v>0.1570249050855637</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.002467429963871837</v>
+        <v>0.05438567325472832</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.004171757493168116</v>
+        <v>0.1538895517587662</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001246099593117833</v>
+        <v>0.1007155776023865</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0004745200858451426</v>
+        <v>0.1591239720582962</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.00514746131375432</v>
+        <v>0.3061573803424835</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.003619607072323561</v>
+        <v>0.0535382553935051</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.002314295619726181</v>
+        <v>0.1039316356182098</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002874167868867517</v>
+        <v>0.09476704895496368</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.01078655105084181</v>
+        <v>0.2387785464525223</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.002958533354103565</v>
+        <v>0.284993976354599</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001210719463415444</v>
+        <v>0.0425911657512188</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.004945914726704359</v>
+        <v>0.2516269683837891</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01143129914999008</v>
+        <v>0.5530235171318054</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.002320824190974236</v>
+        <v>0.4392648041248322</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.004075859673321247</v>
+        <v>0.1627767980098724</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002230416750535369</v>
+        <v>0.09723777323961258</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0004477684269659221</v>
+        <v>0.03116178140044212</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.006079759448766708</v>
+        <v>0.2737659513950348</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002116275019943714</v>
+        <v>0.03963150084018707</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.002971755340695381</v>
+        <v>0.0005013987538404763</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001408998854458332</v>
+        <v>0.04586031287908554</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.003463379107415676</v>
+        <v>0.2671528458595276</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.001834273687563837</v>
+        <v>0.09503938257694244</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001324929762631655</v>
+        <v>0.08085399121046066</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0008810212602838874</v>
+        <v>0.009124359115958214</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.005476773716509342</v>
+        <v>0.1632770001888275</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001805038307793438</v>
+        <v>0.580615758895874</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0004143262049183249</v>
+        <v>0.420295923948288</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.007169747725129128</v>
+        <v>0.3857827186584473</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.005878661759197712</v>
+        <v>0.08949068188667297</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0009862902807071805</v>
+        <v>0.2820225358009338</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0009476577397435904</v>
+        <v>0.02876319922506809</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.007490112446248531</v>
+        <v>0.2172345519065857</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.004250676836818457</v>
+        <v>0.1544679552316666</v>
       </c>
       <c r="CV8" t="n">
-        <v>3.949416714021936e-05</v>
+        <v>0.004725567996501923</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.005052943248301744</v>
+        <v>0.2476718723773956</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.002989114727824926</v>
+        <v>0.01303786132484674</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.004234193824231625</v>
+        <v>0.02066696062684059</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0006465815822593868</v>
+        <v>0.002792881801724434</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.004472160711884499</v>
+        <v>0.2434193342924118</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0006863863673061132</v>
+        <v>0.09946903586387634</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.003008037572726607</v>
+        <v>0.01911234483122826</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0009924683254212141</v>
+        <v>0.02640721574425697</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.004647429566830397</v>
+        <v>0.3844178318977356</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.004030854906886816</v>
+        <v>0.15601646900177</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.002233545994386077</v>
+        <v>0.237905353307724</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0008086091838777065</v>
+        <v>0.1426079124212265</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.004095972515642643</v>
+        <v>0.1040672585368156</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.000231665326282382</v>
+        <v>0.3446142673492432</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.007141318172216415</v>
+        <v>0.1363874971866608</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.01005426980555058</v>
+        <v>0.2144532203674316</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.002735164482146502</v>
+        <v>0.2809107005596161</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.002104221843183041</v>
+        <v>0.03448968380689621</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.000563342880923301</v>
+        <v>0.09937009215354919</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.004520193673670292</v>
+        <v>0.06890381872653961</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.00267790537327528</v>
+        <v>0.1636680066585541</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.002136470517143607</v>
+        <v>0.02026375755667686</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001304563134908676</v>
+        <v>0.0950772762298584</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.003627121215686202</v>
+        <v>0.0633387491106987</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0002205417258664966</v>
+        <v>0.08700671792030334</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0004718152340501547</v>
+        <v>0.002060210332274437</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0008472429472021759</v>
+        <v>0.08926946669816971</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.006033332087099552</v>
+        <v>0.1771149188280106</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.003484636312350631</v>
+        <v>0.008353959769010544</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.00368529511615634</v>
+        <v>0.02791965380311012</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.003590889740735292</v>
+        <v>0.07717815041542053</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.003339777234941721</v>
+        <v>0.1975846886634827</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.000212423678021878</v>
+        <v>0.03203839063644409</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0005759161431342363</v>
+        <v>0.132103219628334</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001337783527560532</v>
+        <v>0.2137639224529266</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0009760473622009158</v>
+        <v>0.1221620291471481</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.003863468067720532</v>
+        <v>0.1176291257143021</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0003637054760474712</v>
+        <v>0.1387064903974533</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.002232682192698121</v>
+        <v>0.03700704500079155</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.000541781831998378</v>
+        <v>0.01529240980744362</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.001402585185132921</v>
+        <v>0.3243095576763153</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.006012204568833113</v>
+        <v>0.004544350318610668</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0009934966219589114</v>
+        <v>0.002769301645457745</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.002298356965184212</v>
+        <v>0.005873656366020441</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0008368442067876458</v>
+        <v>0.04003628343343735</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0008338289335370064</v>
+        <v>0.1593861281871796</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.003451616270467639</v>
+        <v>0.1983401924371719</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0004713901726063341</v>
+        <v>0.1320274025201797</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.001177419675514102</v>
+        <v>0.1664836853742599</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.00354140717536211</v>
+        <v>0.2636152803897858</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.001357646426185966</v>
+        <v>0.03842181339859962</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.002845743205398321</v>
+        <v>0.04157798737287521</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.001155926147475839</v>
+        <v>0.04646749049425125</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0003054560802411288</v>
+        <v>0.01382437907159328</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.005179792176932096</v>
+        <v>0.2585821449756622</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.00151041301432997</v>
+        <v>0.019212506711483</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.001631023129448295</v>
+        <v>0.02442017570137978</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0007939672796055675</v>
+        <v>0.08965131640434265</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.004544752649962902</v>
+        <v>0.2658267617225647</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.000999101554043591</v>
+        <v>0.0924728587269783</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001455408520996571</v>
+        <v>0.09447702020406723</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0001683315495029092</v>
+        <v>0.02350201830267906</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.001569828717038035</v>
+        <v>0.1484846472740173</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.002251866506412625</v>
+        <v>0.1125607490539551</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.004054673481732607</v>
+        <v>0.1158381551504135</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.01021334063261747</v>
+        <v>0.06467971950769424</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.00345669942907989</v>
+        <v>0.05813494324684143</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.00710664689540863</v>
+        <v>0.2764460146427155</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.00204665120691061</v>
+        <v>0.2287724018096924</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.002647534478455782</v>
+        <v>0.1942262053489685</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.002626366214826703</v>
+        <v>0.2121858298778534</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.004270800855010748</v>
+        <v>0.330361396074295</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01347257848829031</v>
+        <v>0.2156347334384918</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0006332994671538472</v>
+        <v>0.03421682864427567</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.005327006336301565</v>
+        <v>0.3233775198459625</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001126233022660017</v>
+        <v>0.22322678565979</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.001655665109865367</v>
+        <v>0.2251857817173004</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.005042379721999168</v>
+        <v>0.01573575474321842</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.003066655481234193</v>
+        <v>0.1848260909318924</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.006066081114113331</v>
+        <v>0.009374896995723248</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0037393260281533</v>
+        <v>0.282229483127594</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0006317705265246332</v>
+        <v>0.03969266265630722</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0002222564799012616</v>
+        <v>0.07664214819669724</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.004115466494113207</v>
+        <v>0.02905724383890629</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.007882362231612206</v>
+        <v>0.339762955904007</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.006293771788477898</v>
+        <v>0.2820146083831787</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.007132601458579302</v>
+        <v>0.04316481202840805</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.001695864950306714</v>
+        <v>0.01416243799030781</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0001965903793461621</v>
+        <v>0.3568383157253265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.823511749738827e-06</v>
+        <v>0.03599750623106956</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001294009038247168</v>
+        <v>0.3124205470085144</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001696430845186114</v>
+        <v>0.03283176198601723</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0007144158589653671</v>
+        <v>0.3133884072303772</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000254107842920348</v>
+        <v>0.1581370681524277</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001157313090516254</v>
+        <v>0.105793334543705</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001272389345103875</v>
+        <v>0.1072206422686577</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001164784262073226</v>
+        <v>0.1182232871651649</v>
       </c>
       <c r="I9" t="n">
-        <v>3.272085814387538e-05</v>
+        <v>0.008564232848584652</v>
       </c>
       <c r="J9" t="n">
-        <v>9.410698839928955e-05</v>
+        <v>0.1136568337678909</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001048690523020923</v>
+        <v>0.321370393037796</v>
       </c>
       <c r="L9" t="n">
-        <v>6.601414497708902e-05</v>
+        <v>0.08580978959798813</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0006564785726368427</v>
+        <v>0.4740003049373627</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0002431537432130426</v>
+        <v>0.2183499187231064</v>
       </c>
       <c r="O9" t="n">
-        <v>9.200576459988952e-05</v>
+        <v>0.04192516207695007</v>
       </c>
       <c r="P9" t="n">
-        <v>8.053194324020296e-05</v>
+        <v>0.0516890324652195</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001035984314512461</v>
+        <v>0.03540030866861343</v>
       </c>
       <c r="R9" t="n">
-        <v>3.900933006661944e-05</v>
+        <v>0.01377825625240803</v>
       </c>
       <c r="S9" t="n">
-        <v>1.30291264213156e-05</v>
+        <v>0.04384553804993629</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0002040312101598829</v>
+        <v>0.06208598241209984</v>
       </c>
       <c r="U9" t="n">
-        <v>2.819319342961535e-05</v>
+        <v>0.007134644314646721</v>
       </c>
       <c r="V9" t="n">
-        <v>6.930842937435955e-05</v>
+        <v>0.005969730205833912</v>
       </c>
       <c r="W9" t="n">
-        <v>6.823678268119693e-05</v>
+        <v>0.0576716773211956</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001104024195228703</v>
+        <v>0.03237558901309967</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0001168590970337391</v>
+        <v>0.0210441779345274</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.368281250004657e-05</v>
+        <v>0.01732287183403969</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.668139005545527e-05</v>
+        <v>0.02673460356891155</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0002325595996808261</v>
+        <v>0.04613608121871948</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0001678404078120366</v>
+        <v>0.1047022566199303</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.449888233968522e-05</v>
+        <v>0.04539889097213745</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.437034891045187e-05</v>
+        <v>0.006944656372070312</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.60714698722586e-05</v>
+        <v>0.01387587655335665</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001166494039352983</v>
+        <v>0.04010948166251183</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.7507015299052e-05</v>
+        <v>0.02140652574598789</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.994363916921429e-05</v>
+        <v>0.005754014477133751</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.781484388629906e-05</v>
+        <v>0.04032400995492935</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.556943895295262e-05</v>
+        <v>0.0416020005941391</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0001627353194635361</v>
+        <v>0.09996926784515381</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.56921141751809e-05</v>
+        <v>0.03720945119857788</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.230800782854203e-05</v>
+        <v>0.01874027401208878</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.494998625479639e-05</v>
+        <v>0.0152314780279994</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0001326729397987947</v>
+        <v>0.09103581309318542</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.440519089461304e-05</v>
+        <v>0.0264923945069313</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.448578930459917e-05</v>
+        <v>0.03017909079790115</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.87097495351918e-05</v>
+        <v>0.04480633139610291</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0001424267829861492</v>
+        <v>0.04569057747721672</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0008380503859370947</v>
+        <v>0.3426866233348846</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.259754521423019e-06</v>
+        <v>0.05676434189081192</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0002347000117879361</v>
+        <v>0.1680928617715836</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.018027513870038e-05</v>
+        <v>0.1301057785749435</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.15624095289968e-06</v>
+        <v>0.02485537901520729</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.330929419258609e-05</v>
+        <v>0.002636794932186604</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.986848605563864e-05</v>
+        <v>0.04807288572192192</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.270659751957282e-05</v>
+        <v>0.05569155514240265</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.213775587733835e-05</v>
+        <v>0.02308306097984314</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0002678196469787508</v>
+        <v>0.01849260926246643</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.000209379883017391</v>
+        <v>0.06309317797422409</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0001244705927092582</v>
+        <v>0.04004594311118126</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0003388983896002173</v>
+        <v>0.02998397871851921</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.538602610817179e-05</v>
+        <v>0.0646200105547905</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0001426077215000987</v>
+        <v>0.007378369569778442</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0001018608018057421</v>
+        <v>0.09721922874450684</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.698725049616769e-05</v>
+        <v>0.08712128549814224</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0002419076627120376</v>
+        <v>0.01072948426008224</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.408457996556535e-05</v>
+        <v>0.08850882947444916</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.130791406467324e-05</v>
+        <v>0.04896603524684906</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.451924905879423e-05</v>
+        <v>0.03105529025197029</v>
       </c>
       <c r="BP9" t="n">
-        <v>6.45188192720525e-05</v>
+        <v>0.1208436712622643</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.000100279925391078</v>
+        <v>0.01029946003109217</v>
       </c>
       <c r="BR9" t="n">
-        <v>6.451357421610737e-06</v>
+        <v>0.05012434348464012</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.619517388462555e-05</v>
+        <v>0.002706659026443958</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.006757055525668e-05</v>
+        <v>0.007912195287644863</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0001104459952330217</v>
+        <v>0.06064433604478836</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0004191903281025589</v>
+        <v>0.1991560608148575</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0001296212285524234</v>
+        <v>0.01483394484966993</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001077955021173693</v>
+        <v>0.1288792788982391</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0001005595840979367</v>
+        <v>0.07853239774703979</v>
       </c>
       <c r="BZ9" t="n">
-        <v>5.817001147079282e-05</v>
+        <v>0.04914016276597977</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.35818180651404e-05</v>
+        <v>0.04742991551756859</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.304514964635018e-05</v>
+        <v>0.01754637248814106</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.442387191578746e-05</v>
+        <v>0.01326263975352049</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.379017627798021e-05</v>
+        <v>0.01886271312832832</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0001935509353643283</v>
+        <v>0.08699939399957657</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.451011070865206e-05</v>
+        <v>0.0036825155839324</v>
       </c>
       <c r="CG9" t="n">
-        <v>8.918663661461323e-05</v>
+        <v>0.08689777553081512</v>
       </c>
       <c r="CH9" t="n">
-        <v>6.22543302597478e-05</v>
+        <v>0.02708814293146133</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.89520615094807e-05</v>
+        <v>0.002223987132310867</v>
       </c>
       <c r="CJ9" t="n">
-        <v>3.367767203599215e-05</v>
+        <v>0.002347951289266348</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.370492100249976e-05</v>
+        <v>0.03281190991401672</v>
       </c>
       <c r="CL9" t="n">
-        <v>3.761345942621119e-05</v>
+        <v>0.02076351456344128</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0002167884958907962</v>
+        <v>0.03812355175614357</v>
       </c>
       <c r="CN9" t="n">
-        <v>8.899295789888129e-05</v>
+        <v>0.2267921715974808</v>
       </c>
       <c r="CO9" t="n">
-        <v>4.100283331354149e-05</v>
+        <v>0.009185393340885639</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0002022646513069049</v>
+        <v>0.06216943264007568</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0001644006260903552</v>
+        <v>0.06920892745256424</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0001924057578435168</v>
+        <v>0.004818273708224297</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0001029513150569983</v>
+        <v>0.05120930820703506</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0002120906574418768</v>
+        <v>0.03609808161854744</v>
       </c>
       <c r="CU9" t="n">
-        <v>2.301640051882714e-05</v>
+        <v>0.05469007045030594</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.600878360681236e-05</v>
+        <v>0.0003397520631551743</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0001928527199197561</v>
+        <v>0.0871649831533432</v>
       </c>
       <c r="CX9" t="n">
-        <v>6.168787513161078e-05</v>
+        <v>0.009634273126721382</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0001273997913813218</v>
+        <v>0.1018447801470757</v>
       </c>
       <c r="CZ9" t="n">
-        <v>5.741025961469859e-05</v>
+        <v>0.01180347707122564</v>
       </c>
       <c r="DA9" t="n">
-        <v>4.481668656808324e-05</v>
+        <v>0.004674560856074095</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.561127621447667e-05</v>
+        <v>0.003167946822941303</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.096701427944936e-05</v>
+        <v>0.02825935743749142</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.659463669057004e-05</v>
+        <v>0.02210448123514652</v>
       </c>
       <c r="DE9" t="n">
-        <v>6.012302765157074e-05</v>
+        <v>0.05840121209621429</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0002422200050204992</v>
+        <v>0.08629527688026428</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.700873301364481e-05</v>
+        <v>0.07811376452445984</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0003152250137645751</v>
+        <v>0.07007922232151031</v>
       </c>
       <c r="DI9" t="n">
-        <v>3.866215047310106e-05</v>
+        <v>0.01270653586834669</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.509073576424271e-05</v>
+        <v>0.01858938485383987</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0001053261948982254</v>
+        <v>0.03170933201909065</v>
       </c>
       <c r="DL9" t="n">
-        <v>2.677723750821315e-05</v>
+        <v>0.1783376932144165</v>
       </c>
       <c r="DM9" t="n">
-        <v>7.637085946043953e-05</v>
+        <v>0.02504152618348598</v>
       </c>
       <c r="DN9" t="n">
-        <v>7.989551522769034e-05</v>
+        <v>0.03599804267287254</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001085117328329943</v>
+        <v>0.03444825857877731</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0001168840753962286</v>
+        <v>0.03653788566589355</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.717729719530325e-05</v>
+        <v>0.0158004816621542</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0001715574180707335</v>
+        <v>0.08100041002035141</v>
       </c>
       <c r="DS9" t="n">
-        <v>6.036453123670071e-05</v>
+        <v>0.08425314724445343</v>
       </c>
       <c r="DT9" t="n">
-        <v>6.836123702669283e-06</v>
+        <v>0.02014496922492981</v>
       </c>
       <c r="DU9" t="n">
-        <v>3.001902041432913e-05</v>
+        <v>0.009937342256307602</v>
       </c>
       <c r="DV9" t="n">
-        <v>2.929305810539518e-05</v>
+        <v>0.07922323048114777</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.990625969483517e-05</v>
+        <v>0.01149154175072908</v>
       </c>
       <c r="DX9" t="n">
-        <v>3.076062421314418e-05</v>
+        <v>0.05869046226143837</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.898962889565155e-05</v>
+        <v>0.02718394063413143</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.524291191250086e-05</v>
+        <v>0.03135151788592339</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0001556335482746363</v>
+        <v>0.08686313778162003</v>
       </c>
       <c r="EB9" t="n">
-        <v>7.770999945932999e-05</v>
+        <v>0.02874786593019962</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.582328670541756e-05</v>
+        <v>0.01112663652747869</v>
       </c>
       <c r="ED9" t="n">
-        <v>2.924941782112001e-06</v>
+        <v>0.1672159284353256</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.065186916093808e-05</v>
+        <v>0.07758653163909912</v>
       </c>
       <c r="EF9" t="n">
-        <v>6.851598300272599e-06</v>
+        <v>0.0145105067640543</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0001633612992009148</v>
+        <v>0.04230371862649918</v>
       </c>
       <c r="EH9" t="n">
-        <v>4.829297540709376e-05</v>
+        <v>0.0004620011895895004</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0001379645837005228</v>
+        <v>0.131639763712883</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0001008797116810456</v>
+        <v>0.01380239147692919</v>
       </c>
       <c r="EK9" t="n">
-        <v>7.937008194858208e-05</v>
+        <v>0.02991512417793274</v>
       </c>
       <c r="EL9" t="n">
-        <v>4.598794839694165e-05</v>
+        <v>0.0005298545584082603</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.290502223127987e-05</v>
+        <v>0.03139185905456543</v>
       </c>
       <c r="EN9" t="n">
-        <v>4.299995453038719e-06</v>
+        <v>0.01644077897071838</v>
       </c>
       <c r="EO9" t="n">
-        <v>4.805369098903611e-05</v>
+        <v>0.01824315264821053</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0001638709509279579</v>
+        <v>0.06827399879693985</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0001462561922380701</v>
+        <v>0.02462176978588104</v>
       </c>
       <c r="ER9" t="n">
-        <v>5.920120383962058e-05</v>
+        <v>0.05041459575295448</v>
       </c>
       <c r="ES9" t="n">
-        <v>4.262166112312116e-05</v>
+        <v>0.004995410330593586</v>
       </c>
       <c r="ET9" t="n">
-        <v>7.895428279880434e-05</v>
+        <v>0.1007838845252991</v>
       </c>
       <c r="EU9" t="n">
-        <v>6.939255399629474e-05</v>
+        <v>0.02828720770776272</v>
       </c>
       <c r="EV9" t="n">
-        <v>5.971291830064729e-05</v>
+        <v>0.02010008320212364</v>
       </c>
       <c r="EW9" t="n">
-        <v>1.797905042622006e-06</v>
+        <v>0.0687335729598999</v>
       </c>
       <c r="EX9" t="n">
-        <v>2.424825652269647e-06</v>
+        <v>0.01892774552106857</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0002082235441775993</v>
+        <v>0.10381730645895</v>
       </c>
       <c r="EZ9" t="n">
-        <v>1.48757417264278e-05</v>
+        <v>0.008881742134690285</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001075558830052614</v>
+        <v>0.1007159352302551</v>
       </c>
       <c r="FB9" t="n">
-        <v>5.584019891102798e-05</v>
+        <v>0.01183701772242785</v>
       </c>
       <c r="FC9" t="n">
-        <v>6.001349902362563e-05</v>
+        <v>0.001500116661190987</v>
       </c>
       <c r="FD9" t="n">
-        <v>4.23825295001734e-05</v>
+        <v>0.00694899819791317</v>
       </c>
       <c r="FE9" t="n">
-        <v>1.887572580017149e-05</v>
+        <v>0.03762975707650185</v>
       </c>
       <c r="FF9" t="n">
-        <v>3.883754470734857e-05</v>
+        <v>0.02567613497376442</v>
       </c>
       <c r="FG9" t="n">
-        <v>1.54512636072468e-05</v>
+        <v>0.04250547289848328</v>
       </c>
       <c r="FH9" t="n">
-        <v>7.852667476981878e-05</v>
+        <v>0.004380093421787024</v>
       </c>
       <c r="FI9" t="n">
-        <v>7.164576345530804e-06</v>
+        <v>0.03614111244678497</v>
       </c>
       <c r="FJ9" t="n">
-        <v>9.125861106440425e-05</v>
+        <v>0.03212177380919456</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001233065850101411</v>
+        <v>0.04809824004769325</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0001122519024647772</v>
+        <v>0.01427541859447956</v>
       </c>
       <c r="FM9" t="n">
-        <v>1.319731654803036e-05</v>
+        <v>0.004770223051309586</v>
       </c>
       <c r="FN9" t="n">
-        <v>8.072922355495393e-06</v>
+        <v>0.04699269682168961</v>
       </c>
       <c r="FO9" t="n">
-        <v>6.81920355418697e-05</v>
+        <v>0.02173374779522419</v>
       </c>
       <c r="FP9" t="n">
-        <v>5.188496288610622e-06</v>
+        <v>0.01808467507362366</v>
       </c>
       <c r="FQ9" t="n">
-        <v>5.417972352006473e-05</v>
+        <v>0.1496128141880035</v>
       </c>
       <c r="FR9" t="n">
-        <v>8.538167458027601e-05</v>
+        <v>0.03288323059678078</v>
       </c>
       <c r="FS9" t="n">
-        <v>2.73038986051688e-05</v>
+        <v>0.09319243580102921</v>
       </c>
       <c r="FT9" t="n">
-        <v>3.419904896873049e-05</v>
+        <v>0.163307398557663</v>
       </c>
       <c r="FU9" t="n">
-        <v>1.493935997132212e-05</v>
+        <v>0.01956319063901901</v>
       </c>
       <c r="FV9" t="n">
-        <v>3.337678572279401e-05</v>
+        <v>0.01805543713271618</v>
       </c>
       <c r="FW9" t="n">
-        <v>1.132966826844495e-05</v>
+        <v>0.06459897011518478</v>
       </c>
       <c r="FX9" t="n">
-        <v>7.153004116844386e-05</v>
+        <v>0.02939709462225437</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0001501408260082826</v>
+        <v>0.01037897076457739</v>
       </c>
       <c r="FZ9" t="n">
-        <v>6.519682938233018e-05</v>
+        <v>0.07254313677549362</v>
       </c>
       <c r="GA9" t="n">
-        <v>1.435969807062065e-05</v>
+        <v>0.06445153057575226</v>
       </c>
       <c r="GB9" t="n">
-        <v>2.772245352389291e-05</v>
+        <v>0.03230603784322739</v>
       </c>
       <c r="GC9" t="n">
-        <v>5.509831680683419e-05</v>
+        <v>0.1443568021059036</v>
       </c>
       <c r="GD9" t="n">
-        <v>6.986921653151512e-05</v>
+        <v>0.02755216509103775</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0002105535386363044</v>
+        <v>0.1123722344636917</v>
       </c>
       <c r="GF9" t="n">
-        <v>3.060804738197476e-05</v>
+        <v>0.02246531471610069</v>
       </c>
       <c r="GG9" t="n">
-        <v>2.87811562884599e-05</v>
+        <v>0.04110264405608177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0138644315302372</v>
+        <v>0.4662731885910034</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01093061547726393</v>
+        <v>0.09520623087882996</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01849553734064102</v>
+        <v>0.2321625649929047</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0005236305296421051</v>
+        <v>0.2390532195568085</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005120988935232162</v>
+        <v>0.1027292162179947</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008609360083937645</v>
+        <v>0.1741020530462265</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001784478081390262</v>
+        <v>0.03790118545293808</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001818226650357246</v>
+        <v>0.07343186438083649</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002575455233454704</v>
+        <v>0.01999251544475555</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005371254868805408</v>
+        <v>0.4771665334701538</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003698237938806415</v>
+        <v>0.04080028086900711</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01448933500796556</v>
+        <v>0.178100124001503</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005909938365221024</v>
+        <v>0.3286164402961731</v>
       </c>
       <c r="N10" t="n">
-        <v>0.008441772311925888</v>
+        <v>0.26711705327034</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001907317317090929</v>
+        <v>0.128566175699234</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001475548837333918</v>
+        <v>0.1054428070783615</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.003590407781302929</v>
+        <v>0.127688929438591</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009582396596670151</v>
+        <v>0.04060526192188263</v>
       </c>
       <c r="S10" t="n">
-        <v>0.005079973489046097</v>
+        <v>0.03157020732760429</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00584515742957592</v>
+        <v>0.486791580915451</v>
       </c>
       <c r="U10" t="n">
-        <v>0.007891510613262653</v>
+        <v>0.1007333844900131</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001676679588854313</v>
+        <v>0.1586178690195084</v>
       </c>
       <c r="W10" t="n">
-        <v>0.000414228648878634</v>
+        <v>0.1230057626962662</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0004865064984187484</v>
+        <v>0.1321650594472885</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0007910989224910736</v>
+        <v>0.1228023022413254</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.000544935290236026</v>
+        <v>0.1252348721027374</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001320086303167045</v>
+        <v>0.04160105064511299</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001374553423374891</v>
+        <v>0.3046118319034576</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.001263990066945553</v>
+        <v>0.1498450934886932</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.002564586699008942</v>
+        <v>0.1576016396284103</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0007690668571740389</v>
+        <v>0.1423673182725906</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00155834446195513</v>
+        <v>0.3939122557640076</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003864492755383253</v>
+        <v>0.2951543033123016</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.001099811168387532</v>
+        <v>0.04357989132404327</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0004527157871052623</v>
+        <v>0.06271401047706604</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.003796444507315755</v>
+        <v>0.0704234391450882</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001176011515781283</v>
+        <v>0.09231109917163849</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.006606587208807468</v>
+        <v>0.4016807079315186</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.001822094665840268</v>
+        <v>0.00966538954526186</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001478726277127862</v>
+        <v>0.04441138356924057</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.003859356744214892</v>
+        <v>0.1429621875286102</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.00561307230964303</v>
+        <v>0.08216876536607742</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.002111619105562568</v>
+        <v>0.1368023455142975</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.120159428566694e-05</v>
+        <v>0.1822925508022308</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001361869741231203</v>
+        <v>0.02066308073699474</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01066760905086994</v>
+        <v>0.2910194396972656</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.002012796932831407</v>
+        <v>0.0437353290617466</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.01235629245638847</v>
+        <v>0.194852203130722</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0005426583811640739</v>
+        <v>0.1840973645448685</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.009810573421418667</v>
+        <v>0.3804034292697906</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0008750061970204115</v>
+        <v>0.2123408317565918</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0007417947053909302</v>
+        <v>0.05579864233732224</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.003540629986673594</v>
+        <v>0.2182961106300354</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.008188573643565178</v>
+        <v>0.1173594146966934</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.005459965206682682</v>
+        <v>0.05268488824367523</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01249944977462292</v>
+        <v>0.1484075486660004</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0006677123019471765</v>
+        <v>0.1158557161688805</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.00471903569996357</v>
+        <v>0.1700590401887894</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.004803315736353397</v>
+        <v>0.07699432224035263</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01649334840476513</v>
+        <v>0.1007285639643669</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002545913448557258</v>
+        <v>0.202317014336586</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.005292655900120735</v>
+        <v>0.1718159317970276</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.008426670916378498</v>
+        <v>0.05833617970347404</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.002181027317419648</v>
+        <v>0.04923680424690247</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.001783492509275675</v>
+        <v>0.01694825291633606</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.004660539329051971</v>
+        <v>0.1399527490139008</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.003913948312401772</v>
+        <v>0.1276792734861374</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.001407484291121364</v>
+        <v>0.008243735879659653</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.003942161798477173</v>
+        <v>0.1112227663397789</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.001278503565117717</v>
+        <v>0.03894519805908203</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.001957529922947288</v>
+        <v>0.04561346769332886</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.004012801684439182</v>
+        <v>0.005949657410383224</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.003949792124330997</v>
+        <v>0.0959114134311676</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.004558630753308535</v>
+        <v>0.4676955938339233</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.004415581002831459</v>
+        <v>0.1022007614374161</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0005191832315176725</v>
+        <v>0.05798593536019325</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.007145845796912909</v>
+        <v>0.2635985910892487</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.003466067835688591</v>
+        <v>0.1436391621828079</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.000791923375800252</v>
+        <v>0.09966667741537094</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003071374259889126</v>
+        <v>0.01518530212342739</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.008307399228215218</v>
+        <v>0.05369285121560097</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.00254401215352118</v>
+        <v>0.04788555949926376</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.001952922437340021</v>
+        <v>0.007349388673901558</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002766101388260722</v>
+        <v>0.0305307898670435</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002016701269894838</v>
+        <v>0.07521054893732071</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0004093494790140539</v>
+        <v>0.1205368787050247</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0004208157770335674</v>
+        <v>0.01987470500171185</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0005416945787146688</v>
+        <v>0.04203004390001297</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.00126274861395359</v>
+        <v>0.02946057543158531</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0003250458976253867</v>
+        <v>0.00656873220577836</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.001832805923186243</v>
+        <v>0.1896356046199799</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0004748769570142031</v>
+        <v>0.05231136456131935</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.002386778127402067</v>
+        <v>0.07068806886672974</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.002336540259420872</v>
+        <v>0.0004645697772502899</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.008416206575930119</v>
+        <v>0.2350717782974243</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.001050022430717945</v>
+        <v>0.2551798224449158</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.004052384290844202</v>
+        <v>0.1943355649709702</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0008914847276173532</v>
+        <v>0.1566284447908401</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.003268011612817645</v>
+        <v>0.1062598377466202</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.001112385652959347</v>
+        <v>0.07845341414213181</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.00309548806399107</v>
+        <v>0.05485600233078003</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.002766133984550834</v>
+        <v>0.02012936770915985</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.001724753179587424</v>
+        <v>0.03662120178341866</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0001881196658359841</v>
+        <v>0.0596039816737175</v>
       </c>
       <c r="DA10" t="n">
-        <v>3.028164064744487e-05</v>
+        <v>0.04332908242940903</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0004116234485991299</v>
+        <v>0.03294327110052109</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.000255515769822523</v>
+        <v>0.02740129083395004</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0005393665051087737</v>
+        <v>0.009661792777478695</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001207216526381671</v>
+        <v>0.009486079216003418</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.001342523377388716</v>
+        <v>0.1781134009361267</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.01645747385919094</v>
+        <v>0.223081573843956</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.004729975946247578</v>
+        <v>0.1265233159065247</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001636883825995028</v>
+        <v>0.2158403396606445</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.001581502379849553</v>
+        <v>0.35350501537323</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.002096822950989008</v>
+        <v>0.03763261064887047</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001367412856779993</v>
+        <v>0.3500780165195465</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.004575453698635101</v>
+        <v>0.1878903806209564</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0009429606143385172</v>
+        <v>0.1794927269220352</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.009668684564530849</v>
+        <v>0.09719134122133255</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.001270174630917609</v>
+        <v>0.0265833418816328</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.002471492392942309</v>
+        <v>0.05742708593606949</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001426584902219474</v>
+        <v>0.4022097885608673</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.000160996220074594</v>
+        <v>0.00161193311214447</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.001423719106242061</v>
+        <v>0.04871546849608421</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.00532968807965517</v>
+        <v>0.03823474049568176</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.006777054164558649</v>
+        <v>0.07817739993333817</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0006217446061782539</v>
+        <v>0.1817931532859802</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0002872089971788228</v>
+        <v>0.06355539709329605</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001295826630666852</v>
+        <v>0.04639763012528419</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0002853765618056059</v>
+        <v>0.2260215133428574</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.006693730130791664</v>
+        <v>0.2499922811985016</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.004460523370653391</v>
+        <v>0.1465480029582977</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.001087391516193748</v>
+        <v>0.05630123242735863</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.002775208558887243</v>
+        <v>0.1519618928432465</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.00372658739797771</v>
+        <v>0.08115463703870773</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0001967585412785411</v>
+        <v>0.06338652968406677</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.007812513038516045</v>
+        <v>0.126698762178421</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.007111572660505772</v>
+        <v>0.002485252916812897</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.001080326153896749</v>
+        <v>0.04433690384030342</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.001695071579888463</v>
+        <v>0.0542963445186615</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.004011932760477066</v>
+        <v>0.011251300573349</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.001525531290099025</v>
+        <v>0.1973210275173187</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0004251469799783081</v>
+        <v>0.01764747500419617</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003528696484863758</v>
+        <v>0.07422705739736557</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.003121501533314586</v>
+        <v>0.2093030959367752</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.001528475666418672</v>
+        <v>0.04199812561273575</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.002157868351787329</v>
+        <v>0.05033490434288979</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.001138345338404179</v>
+        <v>0.07357097417116165</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.009923339821398258</v>
+        <v>0.04745670035481453</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0001841349294409156</v>
+        <v>0.05307764559984207</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0006638499326072633</v>
+        <v>0.1420539915561676</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0005219315644353628</v>
+        <v>0.2001541554927826</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.00893146637827158</v>
+        <v>0.02661801874637604</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0004591819597408175</v>
+        <v>0.06308439373970032</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0009209911804646254</v>
+        <v>0.02993979677557945</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.002567592542618513</v>
+        <v>0.02056573703885078</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001361667877063155</v>
+        <v>0.05592925474047661</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0008175999391824007</v>
+        <v>0.1015258654952049</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001712505822069943</v>
+        <v>0.04561147466301918</v>
       </c>
       <c r="FD10" t="n">
-        <v>9.146367665380239e-05</v>
+        <v>0.01136379595845938</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001056240755133331</v>
+        <v>0.02792363986372948</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.000723332108464092</v>
+        <v>0.03779140114784241</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.003092982340604067</v>
+        <v>0.3170898258686066</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.002845217473804951</v>
+        <v>0.001956980675458908</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001009819330647588</v>
+        <v>0.09502813220024109</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.002184812445193529</v>
+        <v>0.1117943301796913</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.003251979826018214</v>
+        <v>0.2678338289260864</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.00118819740600884</v>
+        <v>0.06949508190155029</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.000118750729598105</v>
+        <v>0.1574305295944214</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.003912627231329679</v>
+        <v>0.01303291693329811</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0001104133552871644</v>
+        <v>0.1136069297790527</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.009156115353107452</v>
+        <v>0.2954759001731873</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0005652143154293299</v>
+        <v>0.4437714517116547</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.002932254690676928</v>
+        <v>0.3969452381134033</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.003913824912160635</v>
+        <v>0.05437202751636505</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.003637770190834999</v>
+        <v>0.1633829176425934</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0009204982779920101</v>
+        <v>0.05701807886362076</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.002866326365619898</v>
+        <v>0.1440375596284866</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.00708062993362546</v>
+        <v>0.05297548696398735</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0007099983049556613</v>
+        <v>0.1931477785110474</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001369195990264416</v>
+        <v>0.1571879237890244</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.001914629363454878</v>
+        <v>0.2785358428955078</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.004021221771836281</v>
+        <v>0.02799670398235321</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.002759690862149</v>
+        <v>0.001091687940061092</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.001400674460455775</v>
+        <v>0.03179112076759338</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.003678097622469068</v>
+        <v>0.2178375422954559</v>
       </c>
       <c r="GE10" t="n">
-        <v>7.891387213021517e-05</v>
+        <v>0.0666426420211792</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.003682574722915888</v>
+        <v>0.2907905280590057</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.001837321789935231</v>
+        <v>0.006978137418627739</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0003576758317649364</v>
+        <v>0.1848378032445908</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004413066431879997</v>
+        <v>0.6726935505867004</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0003899218572769314</v>
+        <v>0.1089623868465424</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002659781370311975</v>
+        <v>0.1009037867188454</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0003751817275770009</v>
+        <v>0.1308978199958801</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003832216141745448</v>
+        <v>0.5220687985420227</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003837634285446256</v>
+        <v>0.08208575844764709</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001367612509056926</v>
+        <v>0.2190112769603729</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000260117813013494</v>
+        <v>0.004383359104394913</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0009549490641802549</v>
+        <v>0.1125851348042488</v>
       </c>
       <c r="K11" t="n">
-        <v>0.003894921857863665</v>
+        <v>0.8122602701187134</v>
       </c>
       <c r="L11" t="n">
-        <v>2.449662133585662e-05</v>
+        <v>0.1519219726324081</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002255227882415056</v>
+        <v>0.2302573770284653</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0001303300814470276</v>
+        <v>0.08066545426845551</v>
       </c>
       <c r="O11" t="n">
-        <v>0.003845914732664824</v>
+        <v>0.5031355619430542</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0001954972249222919</v>
+        <v>0.07127372175455093</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0005252542323432863</v>
+        <v>0.01258785650134087</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001388409582432359</v>
+        <v>0.01605565845966339</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002536092360969633</v>
+        <v>0.01782800443470478</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0005913292989134789</v>
+        <v>0.09036171436309814</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0001115080958697945</v>
+        <v>0.07658873498439789</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0003508969384711236</v>
+        <v>0.1036915853619576</v>
       </c>
       <c r="W11" t="n">
-        <v>1.94684362213593e-05</v>
+        <v>0.06050846725702286</v>
       </c>
       <c r="X11" t="n">
-        <v>1.194518335978501e-05</v>
+        <v>0.06308081746101379</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0004588227020576596</v>
+        <v>0.05632412061095238</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0003846182080451399</v>
+        <v>0.1153211444616318</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0003155224549118429</v>
+        <v>0.003045839723199606</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.000150715553900227</v>
+        <v>0.008864756673574448</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0005611689412035048</v>
+        <v>0.07215313613414764</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.113325354002882e-05</v>
+        <v>0.02430492080748081</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.022266901098192e-05</v>
+        <v>0.1781772822141647</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0001088500575860962</v>
+        <v>0.1887368261814117</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0002385048719588667</v>
+        <v>0.04577532410621643</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0003852841909974813</v>
+        <v>0.06954334676265717</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0003723437548615038</v>
+        <v>0.2782892286777496</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.765847264323384e-05</v>
+        <v>0.04134371504187584</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0003830144996754825</v>
+        <v>0.02108804509043694</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0006345284637063742</v>
+        <v>0.1095688045024872</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.729901461862028e-05</v>
+        <v>0.09220482409000397</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0003172623110003769</v>
+        <v>0.05279099196195602</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0004035402380395681</v>
+        <v>0.0449388325214386</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.000829485768917948</v>
+        <v>0.09995976835489273</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0002581182343419641</v>
+        <v>0.126583144068718</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0002455212234053761</v>
+        <v>0.2109555304050446</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0005381774972192943</v>
+        <v>0.04158745333552361</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0002604444453027099</v>
+        <v>0.08558247983455658</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.00268356641754508</v>
+        <v>0.6975470781326294</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.331674088258296e-05</v>
+        <v>0.08265270292758942</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0002927784225903451</v>
+        <v>0.09471380710601807</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0003080246970057487</v>
+        <v>0.178935781121254</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.002272375160828233</v>
+        <v>0.1985561549663544</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.741433051298372e-05</v>
+        <v>0.05116585269570351</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0006950328242965043</v>
+        <v>0.009087409824132919</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0005030675092712045</v>
+        <v>0.03101521544158459</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0003105735231656581</v>
+        <v>0.01610717177391052</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0009861477883532643</v>
+        <v>0.02316391654312611</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.001307946746237576</v>
+        <v>0.1206250935792923</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0009282813407480717</v>
+        <v>0.07559674233198166</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.001401955261826515</v>
+        <v>0.01423238031566143</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001287491177208722</v>
+        <v>0.1801982074975967</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0001831685949582607</v>
+        <v>0.008263912051916122</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0008186239865608513</v>
+        <v>0.08134987950325012</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0001272512890864164</v>
+        <v>0.008788781240582466</v>
       </c>
       <c r="BL11" t="n">
-        <v>3.102047412539832e-05</v>
+        <v>0.03859294950962067</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0006959366728551686</v>
+        <v>0.1306554824113846</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0004851249395869672</v>
+        <v>0.05045543238520622</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0005878815427422523</v>
+        <v>0.0496760681271553</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.207898407708853e-05</v>
+        <v>0.03058512695133686</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.844905247911811e-05</v>
+        <v>0.05944708734750748</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0003159702173434198</v>
+        <v>0.2218312472105026</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0001473735901527107</v>
+        <v>0.064885213971138</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.208164945244789e-05</v>
+        <v>0.0452723428606987</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0001717881532385945</v>
+        <v>0.02092903852462769</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.001417598221451044</v>
+        <v>0.4355400502681732</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0005283127538859844</v>
+        <v>0.08100597560405731</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0002184933691751212</v>
+        <v>0.1032889038324356</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0001702966110315174</v>
+        <v>0.00818789005279541</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0009201499633491039</v>
+        <v>0.1801897585391998</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0003582877689041197</v>
+        <v>0.1068300381302834</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0004639008548110723</v>
+        <v>0.05438390374183655</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0004458862531464547</v>
+        <v>0.01406166236847639</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.529254950582981e-05</v>
+        <v>0.01730209775269032</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0007792446413077414</v>
+        <v>0.1998710632324219</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.000459841568954289</v>
+        <v>0.02087945118546486</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0004410577239468694</v>
+        <v>0.0255479421466589</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0002834128099493682</v>
+        <v>0.0279704611748457</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0005716999294236302</v>
+        <v>0.1305017918348312</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0002122257428709418</v>
+        <v>0.04068747907876968</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0002280465268995613</v>
+        <v>0.05054668709635735</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0002568097261246294</v>
+        <v>0.02037618309259415</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0005444076377898455</v>
+        <v>0.1718423515558243</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0002289735857630149</v>
+        <v>0.3233487606048584</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001900369388749823</v>
+        <v>0.1602868139743805</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0007400715257972479</v>
+        <v>0.226889044046402</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0003566848754417151</v>
+        <v>0.09338856488466263</v>
       </c>
       <c r="CR11" t="n">
-        <v>3.505607310216874e-05</v>
+        <v>0.07221204787492752</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.000664816761855036</v>
+        <v>0.03435030579566956</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.000760538037866354</v>
+        <v>0.04709581658244133</v>
       </c>
       <c r="CU11" t="n">
-        <v>6.697910430375487e-05</v>
+        <v>0.01697942987084389</v>
       </c>
       <c r="CV11" t="n">
-        <v>3.054773696931079e-05</v>
+        <v>0.02233583852648735</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0006554624415002763</v>
+        <v>0.1937211155891418</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0004532853199634701</v>
+        <v>0.03469798713922501</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0006313059711828828</v>
+        <v>0.04626388475298882</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002497412206139416</v>
+        <v>0.0474369153380394</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0006277664215303957</v>
+        <v>0.1291850358247757</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0001935843756655231</v>
+        <v>0.02574792876839638</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0004358621663413942</v>
+        <v>0.02831839770078659</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0001658840046729892</v>
+        <v>0.008575026877224445</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.000434339395724237</v>
+        <v>0.06890870630741119</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0006741550168953836</v>
+        <v>0.1361083984375</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0001523747923783958</v>
+        <v>0.1230642646551132</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0009352384367957711</v>
+        <v>0.07580803334712982</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0001346544595435262</v>
+        <v>0.2480250895023346</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.421722117811441e-05</v>
+        <v>0.1452850252389908</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0003830729983747005</v>
+        <v>0.05086962133646011</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.001042061252519488</v>
+        <v>0.03022173792123795</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0005183071480132639</v>
+        <v>0.108806312084198</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0002475740620866418</v>
+        <v>0.05333931744098663</v>
       </c>
       <c r="DO11" t="n">
-        <v>9.559272439219058e-05</v>
+        <v>0.1176865845918655</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.000361041456926614</v>
+        <v>0.05224376171827316</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0004908780101686716</v>
+        <v>0.0672878697514534</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.000214561223401688</v>
+        <v>0.03530898317694664</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0002909348986577243</v>
+        <v>0.07458210736513138</v>
       </c>
       <c r="DT11" t="n">
-        <v>6.513047264888883e-05</v>
+        <v>0.002172474749386311</v>
       </c>
       <c r="DU11" t="n">
-        <v>9.916722774505615e-05</v>
+        <v>0.04046832770109177</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0004738043644465506</v>
+        <v>0.02632071822881699</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.000204243857297115</v>
+        <v>0.07996483147144318</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0004341471067164093</v>
+        <v>0.004265045281499624</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0004964798572473228</v>
+        <v>0.03200560063123703</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0004225823795422912</v>
+        <v>0.005694669671356678</v>
       </c>
       <c r="EA11" t="n">
-        <v>2.261323970742524e-05</v>
+        <v>0.02080187015235424</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0001131541866925545</v>
+        <v>0.02032321132719517</v>
       </c>
       <c r="EC11" t="n">
-        <v>8.755750604905188e-05</v>
+        <v>0.02185856364667416</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0001064533498720266</v>
+        <v>0.002807522425428033</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0001994838239625096</v>
+        <v>0.2060876786708832</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0002763186348602176</v>
+        <v>0.006988756358623505</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0005917700473219156</v>
+        <v>0.06340257823467255</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0003495093842502683</v>
+        <v>0.02845194190740585</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0001524965045973659</v>
+        <v>0.03671238571405411</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0001548206637380645</v>
+        <v>0.1094231754541397</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0004598486411850899</v>
+        <v>0.1028990000486374</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0004446595266927034</v>
+        <v>0.01679119095206261</v>
       </c>
       <c r="EM11" t="n">
-        <v>5.072214480605908e-05</v>
+        <v>0.006529462523758411</v>
       </c>
       <c r="EN11" t="n">
-        <v>5.118267654324882e-05</v>
+        <v>0.01470213662832975</v>
       </c>
       <c r="EO11" t="n">
-        <v>2.011992910411209e-05</v>
+        <v>0.0205733198672533</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0004790997772943228</v>
+        <v>0.1007906943559647</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0005220153834670782</v>
+        <v>0.07484160363674164</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0004985442501492798</v>
+        <v>0.02059902809560299</v>
       </c>
       <c r="ES11" t="n">
-        <v>6.502107135020196e-05</v>
+        <v>0.1193719804286957</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0001282930024899542</v>
+        <v>0.0576055683195591</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0002171162341255695</v>
+        <v>0.02404197677969933</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.0006556421867571771</v>
+        <v>0.007601533085107803</v>
       </c>
       <c r="EW11" t="n">
-        <v>5.513775613508187e-05</v>
+        <v>0.07276414334774017</v>
       </c>
       <c r="EX11" t="n">
-        <v>9.114742715610191e-05</v>
+        <v>0.007458940148353577</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0006605559028685093</v>
+        <v>0.2197502851486206</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.000316755089443177</v>
+        <v>0.02348629012703896</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0004411014087963849</v>
+        <v>0.03680649399757385</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0002779463247861713</v>
+        <v>0.06951331347227097</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0005503655411303043</v>
+        <v>0.1129349544644356</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.000310226809233427</v>
+        <v>0.04175162315368652</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0002238182350993156</v>
+        <v>0.04192906245589256</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.00037050386890769</v>
+        <v>0.01360948942601681</v>
       </c>
       <c r="FG11" t="n">
-        <v>5.380483707995154e-05</v>
+        <v>0.0310904998332262</v>
       </c>
       <c r="FH11" t="n">
-        <v>4.463698860490695e-05</v>
+        <v>0.2040281444787979</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0004465189413167536</v>
+        <v>0.07748928666114807</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0008967603789642453</v>
+        <v>0.1286448836326599</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0001753614342305809</v>
+        <v>0.09729735553264618</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.000647535955067724</v>
+        <v>0.1610469222068787</v>
       </c>
       <c r="FM11" t="n">
-        <v>7.588746666442603e-05</v>
+        <v>0.06683795154094696</v>
       </c>
       <c r="FN11" t="n">
-        <v>8.096892270259559e-05</v>
+        <v>0.192633718252182</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0001702774316072464</v>
+        <v>0.1178552061319351</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.000248453114181757</v>
+        <v>0.006488993763923645</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0007112018647603691</v>
+        <v>0.2229177057743073</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.00023469133884646</v>
+        <v>0.03690847754478455</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.000497769913636148</v>
+        <v>0.09804324060678482</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0008623117464594543</v>
+        <v>0.02359385974705219</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0006239975336939096</v>
+        <v>0.06512638926506042</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0002477738598827273</v>
+        <v>0.0709146186709404</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0004441419150680304</v>
+        <v>0.04662341624498367</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0002198592410422862</v>
+        <v>0.03486954420804977</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.0008081052801571786</v>
+        <v>0.1126048117876053</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0002261734916828573</v>
+        <v>0.06343667954206467</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0001771725801518187</v>
+        <v>0.09529902040958405</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0001119507942348719</v>
+        <v>0.002308599185198545</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0004062886291649193</v>
+        <v>0.1770215183496475</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.000605235283728689</v>
+        <v>0.06711393594741821</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.00177553272806108</v>
+        <v>0.1063612103462219</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0001042697113007307</v>
+        <v>0.03607769683003426</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0004374046402517706</v>
+        <v>0.0525510162115097</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.001631011604331434</v>
+        <v>0.182080939412117</v>
       </c>
       <c r="B12" t="n">
-        <v>0.05258265510201454</v>
+        <v>0.1685872077941895</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004564428701996803</v>
+        <v>0.09614772349596024</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03029516153037548</v>
+        <v>0.4939697682857513</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008293625898659229</v>
+        <v>0.07049744576215744</v>
       </c>
       <c r="F12" t="n">
-        <v>0.002939115278422832</v>
+        <v>0.3409547507762909</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002229410922154784</v>
+        <v>0.1760082542896271</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00287867127917707</v>
+        <v>0.1318845152854919</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002277016174048185</v>
+        <v>0.08292292058467865</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002988692373037338</v>
+        <v>0.2544319629669189</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04221833124756813</v>
+        <v>0.08805070817470551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0007126576965674758</v>
+        <v>0.1065354496240616</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02706176973879337</v>
+        <v>0.5975306034088135</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01333525404334068</v>
+        <v>0.0389687679708004</v>
       </c>
       <c r="O12" t="n">
-        <v>0.007656720001250505</v>
+        <v>0.3432911932468414</v>
       </c>
       <c r="P12" t="n">
-        <v>0.006164485588669777</v>
+        <v>0.1778330504894257</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.005866324063390493</v>
+        <v>0.04033465683460236</v>
       </c>
       <c r="R12" t="n">
-        <v>4.413549322634935e-05</v>
+        <v>0.164649561047554</v>
       </c>
       <c r="S12" t="n">
-        <v>0.003528195200487971</v>
+        <v>0.01140239648520947</v>
       </c>
       <c r="T12" t="n">
-        <v>0.006605323869735003</v>
+        <v>0.01604726910591125</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0009436302352696657</v>
+        <v>0.008973550051450729</v>
       </c>
       <c r="V12" t="n">
-        <v>0.004053851589560509</v>
+        <v>0.002745721722021699</v>
       </c>
       <c r="W12" t="n">
-        <v>0.001200769329443574</v>
+        <v>0.0583980605006218</v>
       </c>
       <c r="X12" t="n">
-        <v>0.004454406909644604</v>
+        <v>0.1145754083991051</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.004926257766783237</v>
+        <v>0.04937101900577545</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.004260387271642685</v>
+        <v>0.01927750930190086</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.003400910180062056</v>
+        <v>0.03226291388273239</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.008690088987350464</v>
+        <v>0.02214092761278152</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.00851831678301096</v>
+        <v>0.01754860207438469</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0004005495575256646</v>
+        <v>0.05393373221158981</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0001370514510199428</v>
+        <v>0.09148495644330978</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0007775723934173584</v>
+        <v>0.02699575200676918</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0001919939531944692</v>
+        <v>0.2069936543703079</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.001504865940660238</v>
+        <v>0.06237125396728516</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.002791892737150192</v>
+        <v>0.09826955199241638</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.001459806924685836</v>
+        <v>0.06708651781082153</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.002028813818469644</v>
+        <v>0.0446678064763546</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.00573381083086133</v>
+        <v>0.06060896441340446</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.002915533259510994</v>
+        <v>0.02198946475982666</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0001924622338265181</v>
+        <v>0.06082741171121597</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.005212377291172743</v>
+        <v>0.1125608533620834</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.003356627654284239</v>
+        <v>0.08326983451843262</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.002414171816781163</v>
+        <v>0.04682334139943123</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.002547925803810358</v>
+        <v>0.06311102211475372</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0008878331282176077</v>
+        <v>0.02423519641160965</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.006063827779144049</v>
+        <v>0.1581179052591324</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.03897935897111893</v>
+        <v>0.1856183260679245</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.001731108641251922</v>
+        <v>0.1392477452754974</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01497779507189989</v>
+        <v>0.1610837876796722</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.006066466215997934</v>
+        <v>0.2335130423307419</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.002266848459839821</v>
+        <v>0.2355558276176453</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.004828343633562326</v>
+        <v>0.007782633882015944</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.002271290402859449</v>
+        <v>0.01109842583537102</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0011214897967875</v>
+        <v>0.156405508518219</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.004874574951827526</v>
+        <v>0.03445176407694817</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01140868943184614</v>
+        <v>0.03888564184308052</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.01070741936564445</v>
+        <v>0.05034404620528221</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.001879339339211583</v>
+        <v>0.01481115445494652</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.007793859578669071</v>
+        <v>0.1508663445711136</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.007163204252719879</v>
+        <v>0.02538968622684479</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.004192670341581106</v>
+        <v>0.06374488770961761</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.004545011091977358</v>
+        <v>0.01138137094676495</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0008264302741736174</v>
+        <v>0.01623865775763988</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.005526985041797161</v>
+        <v>0.02353696152567863</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.009646239690482616</v>
+        <v>0.01535527221858501</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.007570906076580286</v>
+        <v>0.01117353979498148</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0004087540728505701</v>
+        <v>0.06367971003055573</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.009203525260090828</v>
+        <v>0.0504547618329525</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.005402309820055962</v>
+        <v>0.07225123792886734</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.003734068712219596</v>
+        <v>0.000432710163295269</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.00144021725282073</v>
+        <v>0.01344887726008892</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.001593102002516389</v>
+        <v>0.004182937555015087</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.004495005588978529</v>
+        <v>0.09707573056221008</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.02086789160966873</v>
+        <v>0.1459112912416458</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.005680146627128124</v>
+        <v>0.02380389533936977</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01006750389933586</v>
+        <v>0.1450534760951996</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.001558197196573019</v>
+        <v>0.02128753438591957</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.006147970445454121</v>
+        <v>0.1404490768909454</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.002100277924910188</v>
+        <v>0.0509449876844883</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.002504716394469142</v>
+        <v>0.04324396699666977</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.002609726274386048</v>
+        <v>0.03025247529149055</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0006576785235665739</v>
+        <v>0.1021002978086472</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.007631774060428143</v>
+        <v>0.05871984735131264</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.00335174729116261</v>
+        <v>0.04055367410182953</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.003358197864145041</v>
+        <v>0.1392934620380402</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.001901446143165231</v>
+        <v>0.005321426782757044</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.001129014301113784</v>
+        <v>0.03253831341862679</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.001336365239694715</v>
+        <v>0.02963758446276188</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0008234009146690369</v>
+        <v>0.05527402460575104</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.001329811755567789</v>
+        <v>0.02071919292211533</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.01531808543950319</v>
+        <v>0.1904248744249344</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.00777325127273798</v>
+        <v>0.02203844115138054</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0004324656329117715</v>
+        <v>0.1516715288162231</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.005839881487190723</v>
+        <v>0.09028398990631104</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.007632868364453316</v>
+        <v>0.09151719510555267</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.002727620303630829</v>
+        <v>0.1147188991308212</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.004832196980714798</v>
+        <v>0.07553465664386749</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.01027075294405222</v>
+        <v>0.01693005301058292</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.001135842525400221</v>
+        <v>0.03178852796554565</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0001295178662985563</v>
+        <v>0.1082874909043312</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.007084179203957319</v>
+        <v>0.05729334801435471</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.003893316257745028</v>
+        <v>0.05811585113406181</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.00557202473282814</v>
+        <v>0.1487739980220795</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002250161254778504</v>
+        <v>0.04163220524787903</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.001051834900863469</v>
+        <v>0.03529512509703636</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0005418122746050358</v>
+        <v>0.02265559509396553</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0009528882219456136</v>
+        <v>0.0345936082303524</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0006493075052276254</v>
+        <v>0.02560820057988167</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.006835713982582092</v>
+        <v>0.1248239278793335</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.002083881990984082</v>
+        <v>0.09146218001842499</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.002769574290141463</v>
+        <v>0.01549419760704041</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01921250484883785</v>
+        <v>0.1593867540359497</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.003348784754052758</v>
+        <v>0.05140582844614983</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0005195935955271125</v>
+        <v>0.1882697492837906</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.001329733873717487</v>
+        <v>0.0001755431294441223</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.006194652523845434</v>
+        <v>0.2584841251373291</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0008430337766185403</v>
+        <v>0.09651359915733337</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.004087716341018677</v>
+        <v>0.08191680908203125</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.001890267827548087</v>
+        <v>0.04225901886820793</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.004520085174590349</v>
+        <v>0.006604617461562157</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.003389738732948899</v>
+        <v>0.06695390492677689</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.006596744991838932</v>
+        <v>0.003400854766368866</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.003070289269089699</v>
+        <v>0.1238971501588821</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0028835020493716</v>
+        <v>0.1257906258106232</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0009365746518597007</v>
+        <v>0.05283650383353233</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0007666884339414537</v>
+        <v>0.1369402259588242</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.004725259728729725</v>
+        <v>0.01558160595595837</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01154968235641718</v>
+        <v>0.00113827281165868</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.00131318042986095</v>
+        <v>0.1446377336978912</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.003371210070326924</v>
+        <v>0.04522161558270454</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.008584578521549702</v>
+        <v>0.119325190782547</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.002749745501205325</v>
+        <v>0.07222190499305725</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0009793987264856696</v>
+        <v>0.05959462374448776</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.001229737186804414</v>
+        <v>0.09663966298103333</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0006322922999970615</v>
+        <v>0.1554190665483475</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0002936724340543151</v>
+        <v>0.09957596659660339</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.004892523400485516</v>
+        <v>0.05915818363428116</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.002226049546152353</v>
+        <v>0.02347259595990181</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.005866430234164</v>
+        <v>0.1217005550861359</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.003730978118255734</v>
+        <v>0.05018456652760506</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.002074805554002523</v>
+        <v>0.02265236712992191</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0005821464583277702</v>
+        <v>0.02090031653642654</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.001684350660070777</v>
+        <v>0.02828584238886833</v>
       </c>
       <c r="EN12" t="n">
-        <v>7.283497689059004e-05</v>
+        <v>0.01089673489332199</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.002766004763543606</v>
+        <v>0.06498219817876816</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.005327335093170404</v>
+        <v>0.05235324800014496</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.00554386293515563</v>
+        <v>0.09747473150491714</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.00278739701025188</v>
+        <v>0.131941020488739</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.003389291232451797</v>
+        <v>0.04281171411275864</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.006258055102080107</v>
+        <v>0.1009959056973457</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.001649886835366488</v>
+        <v>0.08443569391965866</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.002793669467791915</v>
+        <v>0.02809135988354683</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.001196946599520743</v>
+        <v>0.1954270601272583</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.001922200201079249</v>
+        <v>0.115506112575531</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.00705179525539279</v>
+        <v>0.0686471238732338</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.002534878207370639</v>
+        <v>0.03216460719704628</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.004063587635755539</v>
+        <v>0.1604196429252625</v>
       </c>
       <c r="FB12" t="n">
-        <v>6.035540718585253e-05</v>
+        <v>0.02017827890813351</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.001945750089362264</v>
+        <v>0.05098457634449005</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.001468529691919684</v>
+        <v>0.003797000274062157</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0003481168241705745</v>
+        <v>0.03924775123596191</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.001355649903416634</v>
+        <v>0.01187402103096247</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.001279784133657813</v>
+        <v>0.01726795732975006</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.005995194427669048</v>
+        <v>0.008185545913875103</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0001275490940315649</v>
+        <v>0.1056448072195053</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.005500463768839836</v>
+        <v>0.0360882468521595</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.002960470737889409</v>
+        <v>0.06986406445503235</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.00327718909829855</v>
+        <v>0.06732317805290222</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.004061101004481316</v>
+        <v>0.03135378286242485</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.001093997620046139</v>
+        <v>0.02201062999665737</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.001304299803450704</v>
+        <v>0.1264340281486511</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.00605685543268919</v>
+        <v>0.01079431921243668</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.007139935623854399</v>
+        <v>0.1146586760878563</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.00273635727353394</v>
+        <v>0.02338354289531708</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001471098978072405</v>
+        <v>0.04626163095235825</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0009803840657696128</v>
+        <v>0.07222915440797806</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.00185603997670114</v>
+        <v>0.05816939473152161</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.001286725979298353</v>
+        <v>0.01013029646128416</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.002065058099105954</v>
+        <v>0.2228485345840454</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.00155271275434643</v>
+        <v>0.05315046757459641</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.005413929000496864</v>
+        <v>0.03921294212341309</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002844048198312521</v>
+        <v>0.05218546092510223</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.003084969241172075</v>
+        <v>0.1049650236964226</v>
       </c>
       <c r="GB12" t="n">
-        <v>3.392997314222157e-05</v>
+        <v>0.2022176384925842</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.003028696402907372</v>
+        <v>0.1310830563306808</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.006452927365899086</v>
+        <v>0.08715661615133286</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.007344287354499102</v>
+        <v>0.1706438362598419</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.001143357832916081</v>
+        <v>0.02505039609968662</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0001104603288695216</v>
+        <v>0.1430666148662567</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.008726856671273708</v>
+        <v>0.02608283795416355</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0007500459905713797</v>
+        <v>0.0004859310574829578</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001812145696021616</v>
+        <v>0.002927261404693127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004704102408140898</v>
+        <v>0.08622892200946808</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001440699561499059</v>
+        <v>0.04119898751378059</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001835231902077794</v>
+        <v>0.01006969157606363</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001328688696958125</v>
+        <v>0.03697944432497025</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005293807480484247</v>
+        <v>0.01873747073113918</v>
       </c>
       <c r="I13" t="n">
-        <v>7.642584387212992e-05</v>
+        <v>0.009527783840894699</v>
       </c>
       <c r="J13" t="n">
-        <v>0.007619220763444901</v>
+        <v>0.009910533204674721</v>
       </c>
       <c r="K13" t="n">
-        <v>4.432047717273235e-06</v>
+        <v>0.0201445147395134</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002400007331743836</v>
+        <v>0.0150747150182724</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001263385638594627</v>
+        <v>0.1173533126711845</v>
       </c>
       <c r="N13" t="n">
-        <v>0.001834360882639885</v>
+        <v>0.01755219697952271</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0006364407599903643</v>
+        <v>0.008739707991480827</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0007380162714980543</v>
+        <v>0.0228772796690464</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001241132500581443</v>
+        <v>0.04627420753240585</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0005122117581777275</v>
+        <v>0.006631973665207624</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001160299172624946</v>
+        <v>0.001000334974378347</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001797402743250132</v>
+        <v>0.01140394899994135</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0005871693138033152</v>
+        <v>0.005982669536024332</v>
       </c>
       <c r="V13" t="n">
-        <v>1.857396273408085e-05</v>
+        <v>0.01303523685783148</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0008790027350187302</v>
+        <v>0.002710101194679737</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0002585913171060383</v>
+        <v>0.02738828025758266</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.825494786724448e-05</v>
+        <v>0.002551327226683497</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001637427601963282</v>
+        <v>0.005064106546342373</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.103412695461884e-05</v>
+        <v>0.0008543664589524269</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0007116590859368443</v>
+        <v>0.00463828444480896</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.001770806033164263</v>
+        <v>0.003428466618061066</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.000380910380044952</v>
+        <v>0.001706567592918873</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0006065571797080338</v>
+        <v>0.01041563227772713</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0005110189085826278</v>
+        <v>0.03773555904626846</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0001325238845311105</v>
+        <v>0.02099801599979401</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0003288221196271479</v>
+        <v>0.0136471213772893</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001072112005203962</v>
+        <v>0.02673163823783398</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0006703610997647047</v>
+        <v>0.02498762123286724</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0009924373589456081</v>
+        <v>0.007462161593139172</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.006638821214437e-05</v>
+        <v>0.02459579519927502</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0003156501334160566</v>
+        <v>0.01670796051621437</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0009740975801832974</v>
+        <v>0.02110623195767403</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001122292480431497</v>
+        <v>0.02581717073917389</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0002637735742609948</v>
+        <v>0.01276499032974243</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0009190941927954555</v>
+        <v>0.02141348458826542</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.001269996631890535</v>
+        <v>0.00352849205955863</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0003681523085106164</v>
+        <v>0.007265193853527308</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.005151258315891027</v>
+        <v>0.01428412646055222</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.00190118548925966</v>
+        <v>0.00827447883784771</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001959798391908407</v>
+        <v>0.006137856747955084</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.003128346987068653</v>
+        <v>0.05525501817464828</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.002139674965292215</v>
+        <v>0.01719208806753159</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0003031369997188449</v>
+        <v>0.01806704886257648</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0007349535007961094</v>
+        <v>0.01193704456090927</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.002538570901378989</v>
+        <v>0.01189206074923277</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0005447471630759537</v>
+        <v>0.0113714188337326</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.003492813091725111</v>
+        <v>0.03172097355127335</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.003955780528485775</v>
+        <v>0.02231689915060997</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0003138154279440641</v>
+        <v>0.001334665808826685</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0004518122877925634</v>
+        <v>0.02835692465305328</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.00160653458442539</v>
+        <v>0.02588178217411041</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0002209188824053854</v>
+        <v>0.01744368672370911</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0003270573215559125</v>
+        <v>0.02682063542306423</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002045932458713651</v>
+        <v>0.01861710660159588</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.001378066837787628</v>
+        <v>0.04648781940340996</v>
       </c>
       <c r="BL13" t="n">
-        <v>3.955031934310682e-05</v>
+        <v>0.002926846733316779</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.001748946728184819</v>
+        <v>0.02650260366499424</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0004503377713263035</v>
+        <v>0.01639846153557301</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0002562919107731432</v>
+        <v>0.01216851733624935</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0001264166203327477</v>
+        <v>0.01906261034309864</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.000683635997120291</v>
+        <v>0.002315925434231758</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0008189999498426914</v>
+        <v>0.002053327392786741</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0004972250899299979</v>
+        <v>0.01179521344602108</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0006685149855911732</v>
+        <v>0.01277282647788525</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.002496735192835331</v>
+        <v>0.004620431922376156</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.386452539823949e-05</v>
+        <v>0.008669537492096424</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0005572762456722558</v>
+        <v>0.008216500282287598</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0009582052007317543</v>
+        <v>0.05481363087892532</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.913532317616045e-05</v>
+        <v>0.00189998943824321</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0003198863996658474</v>
+        <v>0.009578497149050236</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0002617320569697767</v>
+        <v>0.005073871463537216</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.001697497675195336</v>
+        <v>0.001892053987830877</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0005423069233074784</v>
+        <v>0.009750085882842541</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.001628236495889723</v>
+        <v>0.006112352944910526</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.001196420518681407</v>
+        <v>0.00650513032451272</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0001269789063371718</v>
+        <v>0.001916148466989398</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0002652278344612569</v>
+        <v>0.02939322963356972</v>
       </c>
       <c r="CH13" t="n">
-        <v>4.805551725439727e-07</v>
+        <v>0.008777240291237831</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0009884724859148264</v>
+        <v>0.01369531452655792</v>
       </c>
       <c r="CJ13" t="n">
-        <v>8.577987318858504e-05</v>
+        <v>0.002067976631224155</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.001084575313143432</v>
+        <v>0.008879994042217731</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0001397948217345402</v>
+        <v>0.006638386286795139</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.00220827478915453</v>
+        <v>0.005268779583275318</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001115894177928567</v>
+        <v>0.03142803162336349</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0002949742774944752</v>
+        <v>0.009539227932691574</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001450961921364069</v>
+        <v>0.03414325416088104</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.002415457041934133</v>
+        <v>0.02069349959492683</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0008666393696330488</v>
+        <v>0.003277778392657638</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.001456712139770389</v>
+        <v>0.01376781426370144</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.002994580892845988</v>
+        <v>0.00715307891368866</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0002926065644714981</v>
+        <v>0.03716147318482399</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.00139485823456198</v>
+        <v>0.00576223898679018</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.001343815238215029</v>
+        <v>0.006516627967357635</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0003262392419856042</v>
+        <v>0.0003824041050393134</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0004822007613256574</v>
+        <v>0.02955700643360615</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0001956386840902269</v>
+        <v>0.004985494539141655</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0007599495584145188</v>
+        <v>0.01000936608761549</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0002268810203531757</v>
+        <v>0.0004646212328225374</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.000814201426692307</v>
+        <v>0.009841190651059151</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.000135658192448318</v>
+        <v>0.002697381190955639</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.000667214160785079</v>
+        <v>0.003420452587306499</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.001375581137835979</v>
+        <v>0.001409582328051329</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.00128968118224293</v>
+        <v>0.02474677003920078</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.003180108498781919</v>
+        <v>0.02367779985070229</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001634118147194386</v>
+        <v>0.002271431032568216</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0008170779328793287</v>
+        <v>0.008865751326084137</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001216930104419589</v>
+        <v>0.008695190772414207</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.003259417833760381</v>
+        <v>0.06405239552259445</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0003812187351286411</v>
+        <v>0.004153469577431679</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0008750594570301473</v>
+        <v>0.01549771521240473</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0002882290282286704</v>
+        <v>0.01122725382447243</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0003560747718438506</v>
+        <v>0.02098549902439117</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.001532663009129465</v>
+        <v>0.003637801855802536</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.001753511256538332</v>
+        <v>0.001904991921037436</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0008192601962946355</v>
+        <v>0.005605170968919992</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.000668939552269876</v>
+        <v>0.0002391992602497339</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0003564610378816724</v>
+        <v>0.003737360937520862</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0007668957696296275</v>
+        <v>0.03356481716036797</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.001341854920610785</v>
+        <v>0.003034832887351513</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.00075909512815997</v>
+        <v>0.01150675397366285</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0003273108741268516</v>
+        <v>0.04247286170721054</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0005229930975474417</v>
+        <v>0.0003064991906285286</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.001154043362475932</v>
+        <v>0.01056264061480761</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.46292459248798e-05</v>
+        <v>0.01493279170244932</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0006394729716703296</v>
+        <v>0.008086128160357475</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0002274363359902054</v>
+        <v>0.03124650754034519</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0003085503994952887</v>
+        <v>0.01908943057060242</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.00188871962018311</v>
+        <v>0.01305955555289984</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.002045644912868738</v>
+        <v>0.006325798109173775</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.001499520149081945</v>
+        <v>0.002473726402968168</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.001923573785461485</v>
+        <v>0.03206436336040497</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.001894310698844492</v>
+        <v>0.00823478028178215</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0002465613069944084</v>
+        <v>0.01390303112566471</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.000244155089603737</v>
+        <v>0.003530497197061777</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0002953885996248573</v>
+        <v>0.007856898009777069</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0001652294595260173</v>
+        <v>0.005868527106940746</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0002150131622329354</v>
+        <v>0.007475239224731922</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.002595276804640889</v>
+        <v>0.00216606492176652</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0004162008117418736</v>
+        <v>0.01454220712184906</v>
       </c>
       <c r="ER13" t="n">
-        <v>8.298899047076702e-06</v>
+        <v>0.04076985269784927</v>
       </c>
       <c r="ES13" t="n">
-        <v>6.135129660833627e-05</v>
+        <v>0.0003907494246959686</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001086076721549034</v>
+        <v>0.03584231808781624</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0008002237300388515</v>
+        <v>0.008513491600751877</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0005495070945471525</v>
+        <v>0.008719218894839287</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.001357631175778806</v>
+        <v>0.01585543900728226</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001452393364161253</v>
+        <v>0.004725066479295492</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.001377551001496613</v>
+        <v>0.001611331710591912</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0004224850563332438</v>
+        <v>0.002478738548234105</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0005031533655710518</v>
+        <v>0.03633590042591095</v>
       </c>
       <c r="FB13" t="n">
-        <v>8.104872540570796e-05</v>
+        <v>0.008514191024005413</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0008256002911366522</v>
+        <v>0.004224380943924189</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0001314667024416849</v>
+        <v>0.001112159341573715</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0009320844546891749</v>
+        <v>0.01089676283299923</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0001966326963156462</v>
+        <v>0.001355553744360805</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001626443699933589</v>
+        <v>0.00507371686398983</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.00165009475313127</v>
+        <v>0.001994245452806354</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.001653300365433097</v>
+        <v>0.00477859890088439</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0009920739103108644</v>
+        <v>0.01291329227387905</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0008573575178161263</v>
+        <v>0.0235875565558672</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.00182410329580307</v>
+        <v>0.002447654958814383</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.001404982293024659</v>
+        <v>0.008370492607355118</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0004490180290304124</v>
+        <v>0.007582373451441526</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0004624438006430864</v>
+        <v>0.02189726009964943</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001550506101921201</v>
+        <v>0.008150964044034481</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.000526453135535121</v>
+        <v>0.008385835215449333</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.001513962866738439</v>
+        <v>0.01336162630468607</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.001019084709696472</v>
+        <v>0.02987473830580711</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.00222277594730258</v>
+        <v>0.029063630849123</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001911144587211311</v>
+        <v>0.01554378680884838</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.001388458535075188</v>
+        <v>0.007963307201862335</v>
       </c>
       <c r="FW13" t="n">
-        <v>2.463252167217433e-05</v>
+        <v>0.01195401418954134</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0001053273881552741</v>
+        <v>0.002139607444405556</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0006813780637457967</v>
+        <v>0.0009579344186931849</v>
       </c>
       <c r="FZ13" t="n">
-        <v>5.613388202618808e-05</v>
+        <v>0.007487102877348661</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0002394372131675482</v>
+        <v>0.003199364524334669</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0001796833821572363</v>
+        <v>0.0435350090265274</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0006687330896966159</v>
+        <v>0.01198379881680012</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0003028829814866185</v>
+        <v>0.005981271155178547</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.001034660963341594</v>
+        <v>0.02320970222353935</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.000537474756129086</v>
+        <v>0.008495230227708817</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0004865268711000681</v>
+        <v>0.00810588151216507</v>
       </c>
     </row>
     <row r="14">
@@ -8965,1709 +8965,1709 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3.938581721740775e-05</v>
+        <v>7.803447488186066e-07</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0003021846059709787</v>
+        <v>2.57437932305038e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>3.120422843494453e-05</v>
+        <v>3.03977060411853e-07</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002281047927681357</v>
+        <v>1.716203428259178e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>7.93904546299018e-05</v>
+        <v>1.86967412219019e-07</v>
       </c>
       <c r="F16" t="n">
-        <v>3.849655331578106e-05</v>
+        <v>2.086546828650171e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>1.432282715541078e-05</v>
+        <v>1.905593762785429e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>1.789332964108326e-05</v>
+        <v>7.185328172454319e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>3.176266909576952e-05</v>
+        <v>5.713179618282993e-08</v>
       </c>
       <c r="J16" t="n">
-        <v>6.250254227779806e-05</v>
+        <v>1.17615535089044e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0002373135212110355</v>
+        <v>2.965985004266258e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>2.31113335757982e-05</v>
+        <v>4.809699021279812e-07</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001756221172399819</v>
+        <v>2.111727781084483e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0001168663802673109</v>
+        <v>1.283609549318498e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0001281439472222701</v>
+        <v>2.012830236708396e-06</v>
       </c>
       <c r="P16" t="n">
-        <v>1.851118213380687e-05</v>
+        <v>1.354237895156984e-07</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.765826062997803e-05</v>
+        <v>3.579343399451318e-08</v>
       </c>
       <c r="R16" t="n">
-        <v>2.403919825155754e-05</v>
+        <v>8.977031029644422e-08</v>
       </c>
       <c r="S16" t="n">
-        <v>6.472946552094072e-07</v>
+        <v>2.625495767460961e-07</v>
       </c>
       <c r="T16" t="n">
-        <v>5.370980215957388e-05</v>
+        <v>4.404926983170299e-07</v>
       </c>
       <c r="U16" t="n">
-        <v>8.314951628562994e-06</v>
+        <v>2.247766985874478e-07</v>
       </c>
       <c r="V16" t="n">
-        <v>2.22700837184675e-05</v>
+        <v>3.32081867782108e-07</v>
       </c>
       <c r="W16" t="n">
-        <v>4.622135020326823e-05</v>
+        <v>6.396217600013188e-07</v>
       </c>
       <c r="X16" t="n">
-        <v>4.22601806349121e-05</v>
+        <v>6.629652489209548e-07</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.220797174843028e-05</v>
+        <v>7.438006264237629e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.530331948946696e-05</v>
+        <v>5.716092914553883e-07</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.903340959572233e-05</v>
+        <v>1.06413054368204e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.150895332102664e-05</v>
+        <v>9.083852603453124e-08</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.939806265407242e-05</v>
+        <v>4.982214818483044e-08</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.657141910982318e-05</v>
+        <v>2.17706286775865e-07</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.342184234294109e-05</v>
+        <v>9.407455650034535e-07</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.524795127101243e-05</v>
+        <v>5.580363335866423e-07</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.513919182296377e-07</v>
+        <v>5.656358439409814e-07</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.216517507098615e-05</v>
+        <v>4.445485615178768e-07</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.076017936924472e-06</v>
+        <v>9.632155979488743e-07</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.556539473313023e-06</v>
+        <v>1.442294035314262e-07</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.750983523786999e-05</v>
+        <v>4.281066026123881e-07</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.360714279348031e-05</v>
+        <v>4.215444846522587e-07</v>
       </c>
       <c r="AM16" t="n">
-        <v>9.642541954235639e-06</v>
+        <v>3.2071500299935e-07</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.681501998973545e-05</v>
+        <v>8.903203934096382e-07</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.113126174663194e-05</v>
+        <v>1.087108003616777e-07</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.642022981395712e-06</v>
+        <v>3.285437060185359e-07</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.010850377904717e-05</v>
+        <v>2.218482961779955e-07</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.517483365722001e-06</v>
+        <v>1.426956686145786e-07</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.767196772561874e-05</v>
+        <v>3.331282414364978e-07</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.236675234395079e-05</v>
+        <v>1.280864694308548e-07</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0002054830110864714</v>
+        <v>2.159039922844386e-06</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.48846881731879e-05</v>
+        <v>5.685774908670282e-07</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.243108196533285e-05</v>
+        <v>3.182187242600776e-07</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.396988283086102e-06</v>
+        <v>1.485885604779469e-06</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.570442903670482e-06</v>
+        <v>1.258399720427406e-06</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.793693627405446e-06</v>
+        <v>2.835523815747365e-08</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.134917202871293e-05</v>
+        <v>2.531364202695841e-07</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.422684727003798e-05</v>
+        <v>4.293592326121143e-07</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.116007479140535e-05</v>
+        <v>4.880297410636558e-08</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.862866313080303e-05</v>
+        <v>7.388641733996337e-07</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.234408207703382e-05</v>
+        <v>3.489933249056776e-07</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.085505836177617e-05</v>
+        <v>1.838978676005354e-07</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0001068207275238819</v>
+        <v>9.609877906768816e-07</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.000830085715279e-05</v>
+        <v>1.594083016698278e-07</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.885968049464282e-05</v>
+        <v>4.312236967507488e-08</v>
       </c>
       <c r="BJ16" t="n">
-        <v>6.314777419902384e-05</v>
+        <v>6.724754939568811e-07</v>
       </c>
       <c r="BK16" t="n">
-        <v>2.916161975008436e-06</v>
+        <v>3.779329560416045e-08</v>
       </c>
       <c r="BL16" t="n">
-        <v>5.017024886910804e-05</v>
+        <v>1.082370246763276e-07</v>
       </c>
       <c r="BM16" t="n">
-        <v>4.805466596735641e-05</v>
+        <v>4.73389206945285e-07</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.530626054271124e-05</v>
+        <v>1.411384786820236e-08</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.818376404116862e-05</v>
+        <v>3.411194029467879e-07</v>
       </c>
       <c r="BP16" t="n">
-        <v>7.208785245893523e-05</v>
+        <v>7.50417996187025e-07</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.829168806783855e-05</v>
+        <v>3.73984676116379e-07</v>
       </c>
       <c r="BR16" t="n">
-        <v>1.764354965416715e-05</v>
+        <v>2.276740929119114e-07</v>
       </c>
       <c r="BS16" t="n">
-        <v>5.628234066534787e-05</v>
+        <v>2.088755053364366e-07</v>
       </c>
       <c r="BT16" t="n">
-        <v>1.339830487268046e-05</v>
+        <v>4.662588182213767e-08</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.202912350592669e-06</v>
+        <v>7.738101004406417e-08</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.436059917788953e-05</v>
+        <v>1.143279632742633e-06</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.5394165024627e-05</v>
+        <v>4.352964992904163e-07</v>
       </c>
       <c r="BX16" t="n">
-        <v>2.306576607224997e-05</v>
+        <v>5.680306003341684e-07</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.065336598723661e-06</v>
+        <v>9.982043280842845e-08</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.065652941178996e-05</v>
+        <v>1.078528725884098e-06</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.191345578874461e-05</v>
+        <v>7.125876777536178e-07</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.069085647031898e-05</v>
+        <v>3.471947707112122e-08</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.046001645794604e-05</v>
+        <v>1.484197476031568e-08</v>
       </c>
       <c r="CD16" t="n">
-        <v>1.094849608307413e-06</v>
+        <v>1.584506179597156e-07</v>
       </c>
       <c r="CE16" t="n">
-        <v>5.156280531082302e-05</v>
+        <v>7.80264542754594e-07</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.920091901614796e-05</v>
+        <v>6.195380564122388e-08</v>
       </c>
       <c r="CG16" t="n">
-        <v>1.766169225447811e-05</v>
+        <v>4.888134412794898e-07</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.508739296696149e-05</v>
+        <v>1.92351507166677e-07</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.799091114662588e-05</v>
+        <v>4.556466137728421e-07</v>
       </c>
       <c r="CJ16" t="n">
-        <v>8.120558049995452e-06</v>
+        <v>1.477703506225225e-07</v>
       </c>
       <c r="CK16" t="n">
-        <v>4.534784693532856e-06</v>
+        <v>8.673092111166625e-08</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.477704219927546e-05</v>
+        <v>6.183135781157034e-08</v>
       </c>
       <c r="CM16" t="n">
-        <v>5.281115954858251e-05</v>
+        <v>7.203735208349826e-07</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.812483560570399e-06</v>
+        <v>1.335558522441715e-06</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.732317105052061e-05</v>
+        <v>9.63370098361338e-07</v>
       </c>
       <c r="CP16" t="n">
-        <v>9.588697867002338e-05</v>
+        <v>2.038620152688964e-07</v>
       </c>
       <c r="CQ16" t="n">
-        <v>5.871575558558106e-05</v>
+        <v>2.04410611104322e-07</v>
       </c>
       <c r="CR16" t="n">
-        <v>3.84947270504199e-07</v>
+        <v>7.940948876239418e-08</v>
       </c>
       <c r="CS16" t="n">
-        <v>5.36040315637365e-05</v>
+        <v>1.073506439297489e-07</v>
       </c>
       <c r="CT16" t="n">
-        <v>7.296606327145128e-06</v>
+        <v>1.591814395851543e-07</v>
       </c>
       <c r="CU16" t="n">
-        <v>7.286069831025088e-06</v>
+        <v>1.157615940883261e-07</v>
       </c>
       <c r="CV16" t="n">
-        <v>4.157176590524614e-06</v>
+        <v>4.947463239091121e-08</v>
       </c>
       <c r="CW16" t="n">
-        <v>4.649682159652002e-05</v>
+        <v>7.553971954621375e-07</v>
       </c>
       <c r="CX16" t="n">
-        <v>2.754690831352491e-05</v>
+        <v>1.626780914421033e-07</v>
       </c>
       <c r="CY16" t="n">
-        <v>3.47095774486661e-05</v>
+        <v>5.065147661298397e-07</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.058893551293295e-05</v>
+        <v>2.891948440719716e-07</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.224368108727504e-05</v>
+        <v>4.794100618710218e-07</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.887118378363084e-05</v>
+        <v>2.002484507102054e-07</v>
       </c>
       <c r="DC16" t="n">
-        <v>9.470424629398622e-06</v>
+        <v>9.521352239971748e-08</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.835455441323575e-05</v>
+        <v>3.997658737375787e-08</v>
       </c>
       <c r="DE16" t="n">
-        <v>4.448447361937724e-05</v>
+        <v>3.68960343166691e-07</v>
       </c>
       <c r="DF16" t="n">
-        <v>6.820575890742475e-06</v>
+        <v>5.459740464175411e-07</v>
       </c>
       <c r="DG16" t="n">
-        <v>7.211080082925037e-05</v>
+        <v>2.010091293414007e-08</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0001314687251579016</v>
+        <v>4.256196461938089e-07</v>
       </c>
       <c r="DI16" t="n">
-        <v>6.850632780697197e-05</v>
+        <v>5.377481784307747e-07</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.85544940904947e-05</v>
+        <v>7.26307575860119e-07</v>
       </c>
       <c r="DK16" t="n">
-        <v>2.215092536062002e-06</v>
+        <v>8.955026942203403e-08</v>
       </c>
       <c r="DL16" t="n">
-        <v>3.739547901204787e-05</v>
+        <v>6.955569915589876e-07</v>
       </c>
       <c r="DM16" t="n">
-        <v>2.724467776715755e-05</v>
+        <v>3.401621597731719e-07</v>
       </c>
       <c r="DN16" t="n">
-        <v>4.781207280757371e-06</v>
+        <v>5.808740155544001e-08</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.457151120121125e-05</v>
+        <v>6.901741471665446e-07</v>
       </c>
       <c r="DP16" t="n">
-        <v>3.035232293768786e-05</v>
+        <v>1.837046994523917e-07</v>
       </c>
       <c r="DQ16" t="n">
-        <v>5.113438419357408e-06</v>
+        <v>1.59671003530093e-07</v>
       </c>
       <c r="DR16" t="n">
-        <v>2.255491563118994e-05</v>
+        <v>4.85502596347942e-07</v>
       </c>
       <c r="DS16" t="n">
-        <v>1.929897371155676e-05</v>
+        <v>3.692731240789726e-07</v>
       </c>
       <c r="DT16" t="n">
-        <v>1.659138797549531e-05</v>
+        <v>7.145250719986507e-07</v>
       </c>
       <c r="DU16" t="n">
-        <v>8.309239092341159e-07</v>
+        <v>2.000387269163184e-07</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.559327135211788e-05</v>
+        <v>7.814585956111841e-08</v>
       </c>
       <c r="DW16" t="n">
-        <v>1.115959275921341e-05</v>
+        <v>2.432184089684597e-07</v>
       </c>
       <c r="DX16" t="n">
-        <v>3.305147038190626e-05</v>
+        <v>2.996930277276988e-07</v>
       </c>
       <c r="DY16" t="n">
-        <v>5.942285497440025e-05</v>
+        <v>4.815503302779689e-07</v>
       </c>
       <c r="DZ16" t="n">
-        <v>1.759248789312551e-06</v>
+        <v>4.646774698358058e-07</v>
       </c>
       <c r="EA16" t="n">
-        <v>5.380758011597209e-06</v>
+        <v>5.700599672309181e-07</v>
       </c>
       <c r="EB16" t="n">
-        <v>4.458111288840882e-05</v>
+        <v>1.787790182561366e-07</v>
       </c>
       <c r="EC16" t="n">
-        <v>8.864086339599453e-06</v>
+        <v>1.565831553307362e-08</v>
       </c>
       <c r="ED16" t="n">
-        <v>3.635093662524014e-06</v>
+        <v>8.094515351331211e-07</v>
       </c>
       <c r="EE16" t="n">
-        <v>5.023921403335407e-06</v>
+        <v>6.514688379866129e-07</v>
       </c>
       <c r="EF16" t="n">
-        <v>1.337105277343653e-05</v>
+        <v>6.38529229490814e-08</v>
       </c>
       <c r="EG16" t="n">
-        <v>3.652596933534369e-05</v>
+        <v>3.452256009950361e-07</v>
       </c>
       <c r="EH16" t="n">
-        <v>1.510737365606474e-05</v>
+        <v>1.064706935949289e-07</v>
       </c>
       <c r="EI16" t="n">
-        <v>1.813996641431004e-05</v>
+        <v>1.670397011821478e-07</v>
       </c>
       <c r="EJ16" t="n">
-        <v>2.397409116383642e-05</v>
+        <v>3.21160939620313e-07</v>
       </c>
       <c r="EK16" t="n">
-        <v>1.783008701750077e-05</v>
+        <v>3.895491431649134e-07</v>
       </c>
       <c r="EL16" t="n">
-        <v>2.733127621468157e-05</v>
+        <v>2.368733902358144e-07</v>
       </c>
       <c r="EM16" t="n">
-        <v>7.140291927498765e-06</v>
+        <v>1.020177577970571e-07</v>
       </c>
       <c r="EN16" t="n">
-        <v>1.295896981901024e-05</v>
+        <v>5.105485101353224e-08</v>
       </c>
       <c r="EO16" t="n">
-        <v>2.202443283749744e-06</v>
+        <v>1.900752693018148e-07</v>
       </c>
       <c r="EP16" t="n">
-        <v>2.332523035875056e-05</v>
+        <v>3.087969844273175e-07</v>
       </c>
       <c r="EQ16" t="n">
-        <v>3.609917257563211e-05</v>
+        <v>2.273912116379506e-07</v>
       </c>
       <c r="ER16" t="n">
-        <v>1.378840124743874e-06</v>
+        <v>3.772454988393292e-07</v>
       </c>
       <c r="ES16" t="n">
-        <v>1.813139169826172e-05</v>
+        <v>4.585074009355594e-07</v>
       </c>
       <c r="ET16" t="n">
-        <v>2.368650257267291e-06</v>
+        <v>1.957411370767659e-07</v>
       </c>
       <c r="EU16" t="n">
-        <v>1.474063901696354e-05</v>
+        <v>2.190939341062403e-07</v>
       </c>
       <c r="EV16" t="n">
-        <v>6.598746404051781e-05</v>
+        <v>2.972777508603031e-07</v>
       </c>
       <c r="EW16" t="n">
-        <v>1.977475039893761e-05</v>
+        <v>1.956790498525152e-07</v>
       </c>
       <c r="EX16" t="n">
-        <v>4.155568603891879e-06</v>
+        <v>8.303830156819458e-08</v>
       </c>
       <c r="EY16" t="n">
-        <v>4.401256956043653e-05</v>
+        <v>8.398427553402144e-07</v>
       </c>
       <c r="EZ16" t="n">
-        <v>2.181389208999462e-05</v>
+        <v>1.100286510791193e-07</v>
       </c>
       <c r="FA16" t="n">
-        <v>2.108387889165897e-05</v>
+        <v>5.333557737685624e-07</v>
       </c>
       <c r="FB16" t="n">
-        <v>9.288055480283219e-06</v>
+        <v>1.345846101230563e-07</v>
       </c>
       <c r="FC16" t="n">
-        <v>2.208079968113452e-05</v>
+        <v>4.719613571069203e-07</v>
       </c>
       <c r="FD16" t="n">
-        <v>1.436944967281306e-05</v>
+        <v>3.442114149265763e-09</v>
       </c>
       <c r="FE16" t="n">
-        <v>3.321556960145244e-06</v>
+        <v>1.709468762101096e-07</v>
       </c>
       <c r="FF16" t="n">
-        <v>2.813496939779725e-05</v>
+        <v>7.325090223275765e-08</v>
       </c>
       <c r="FG16" t="n">
-        <v>2.358167876082007e-05</v>
+        <v>1.102895765825451e-07</v>
       </c>
       <c r="FH16" t="n">
-        <v>1.318724116572412e-06</v>
+        <v>2.962641190151771e-07</v>
       </c>
       <c r="FI16" t="n">
-        <v>6.225890683708712e-05</v>
+        <v>5.164989147488086e-07</v>
       </c>
       <c r="FJ16" t="n">
-        <v>4.586735667544417e-05</v>
+        <v>2.998329478032247e-07</v>
       </c>
       <c r="FK16" t="n">
-        <v>6.813063464505831e-07</v>
+        <v>2.497840796422679e-07</v>
       </c>
       <c r="FL16" t="n">
-        <v>2.988291089423001e-05</v>
+        <v>2.680392583442881e-07</v>
       </c>
       <c r="FM16" t="n">
-        <v>1.414047619618941e-05</v>
+        <v>7.961473613704584e-08</v>
       </c>
       <c r="FN16" t="n">
-        <v>4.590324169839732e-05</v>
+        <v>2.846574602699548e-07</v>
       </c>
       <c r="FO16" t="n">
-        <v>2.452815533615649e-05</v>
+        <v>5.295660798765311e-07</v>
       </c>
       <c r="FP16" t="n">
-        <v>7.47887816032744e-06</v>
+        <v>9.112922043641447e-07</v>
       </c>
       <c r="FQ16" t="n">
-        <v>5.507817149918992e-06</v>
+        <v>3.874995400110492e-07</v>
       </c>
       <c r="FR16" t="n">
-        <v>4.898054612567648e-06</v>
+        <v>2.774416145712166e-07</v>
       </c>
       <c r="FS16" t="n">
-        <v>8.531941602996085e-06</v>
+        <v>2.54032244129121e-07</v>
       </c>
       <c r="FT16" t="n">
-        <v>5.783413871540688e-05</v>
+        <v>1.227338429998781e-06</v>
       </c>
       <c r="FU16" t="n">
-        <v>4.279172571841627e-07</v>
+        <v>2.795661373511393e-07</v>
       </c>
       <c r="FV16" t="n">
-        <v>3.663825191324577e-05</v>
+        <v>3.848538767670107e-07</v>
       </c>
       <c r="FW16" t="n">
-        <v>4.426034502102993e-05</v>
+        <v>3.16736930017214e-07</v>
       </c>
       <c r="FX16" t="n">
-        <v>3.33032148773782e-05</v>
+        <v>9.710538506624289e-08</v>
       </c>
       <c r="FY16" t="n">
-        <v>6.422966544050723e-05</v>
+        <v>3.072618142141437e-07</v>
       </c>
       <c r="FZ16" t="n">
-        <v>2.827833304763772e-05</v>
+        <v>1.819695967242296e-07</v>
       </c>
       <c r="GA16" t="n">
-        <v>5.087421868665842e-06</v>
+        <v>8.184917987819063e-07</v>
       </c>
       <c r="GB16" t="n">
-        <v>5.48431626157253e-06</v>
+        <v>3.749642587536073e-07</v>
       </c>
       <c r="GC16" t="n">
-        <v>7.776456186547875e-05</v>
+        <v>8.43853626975033e-07</v>
       </c>
       <c r="GD16" t="n">
-        <v>4.688126500695944e-05</v>
+        <v>7.319922588067129e-07</v>
       </c>
       <c r="GE16" t="n">
-        <v>9.919614967657253e-05</v>
+        <v>9.044662192536634e-07</v>
       </c>
       <c r="GF16" t="n">
-        <v>1.980873821594287e-05</v>
+        <v>4.292052153687109e-07</v>
       </c>
       <c r="GG16" t="n">
-        <v>4.861117486143485e-05</v>
+        <v>7.557185455198123e-08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0001127168216044083</v>
+        <v>1.793273529671069e-09</v>
       </c>
       <c r="B17" t="n">
-        <v>0.002944689942523837</v>
+        <v>2.384829445034597e-09</v>
       </c>
       <c r="C17" t="n">
-        <v>1.498403435107321e-05</v>
+        <v>1.303877561475986e-09</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00141638983041048</v>
+        <v>1.662524562462409e-10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0002926437300629914</v>
+        <v>2.861945680443512e-10</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001894774613901973</v>
+        <v>3.454092567523048e-10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001137079525506124</v>
+        <v>2.560448741917298e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001147500006482005</v>
+        <v>3.661636327478845e-09</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0001296392147196457</v>
+        <v>2.55418064476487e-09</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0004295097023714334</v>
+        <v>1.706110697163865e-09</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002793787280097604</v>
+        <v>1.924160386579388e-09</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0001663427538005635</v>
+        <v>1.643943647877677e-09</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001011669053696096</v>
+        <v>1.057631870970965e-09</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0001940586953423917</v>
+        <v>5.070421860153829e-10</v>
       </c>
       <c r="O17" t="n">
-        <v>0.001870084088295698</v>
+        <v>1.8498576281889e-10</v>
       </c>
       <c r="P17" t="n">
-        <v>1.324342156294733e-05</v>
+        <v>1.494224854958759e-09</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0003989445976912975</v>
+        <v>3.294465589220863e-09</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0002862340188585222</v>
+        <v>8.92552864950602e-10</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001401053159497678</v>
+        <v>2.049045377816583e-09</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0002712109999265522</v>
+        <v>2.45608489102267e-09</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0002490077749826014</v>
+        <v>3.896808153935893e-10</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0002226656652055681</v>
+        <v>8.479972279928916e-10</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0003833667142316699</v>
+        <v>2.71035749399573e-10</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0002230819809483364</v>
+        <v>1.016028372546884e-09</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0001721523294690996</v>
+        <v>9.022001895564458e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0004890099517069757</v>
+        <v>1.208126820806399e-09</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0003892708627972752</v>
+        <v>2.093606621400568e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0001041484501911327</v>
+        <v>1.966280471776827e-09</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.969993071630597e-05</v>
+        <v>5.62713986518304e-10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0001049902566592209</v>
+        <v>8.665859141387955e-10</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.424633541726507e-05</v>
+        <v>1.215877176719005e-09</v>
       </c>
       <c r="AF17" t="n">
-        <v>4.305804031901062e-05</v>
+        <v>8.477281099317224e-10</v>
       </c>
       <c r="AG17" t="n">
-        <v>8.483503188472241e-05</v>
+        <v>1.701233598438989e-09</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0001538851065561175</v>
+        <v>3.72917058344413e-10</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0002240717585664243</v>
+        <v>9.075047935347413e-10</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.239999205106869e-05</v>
+        <v>2.044958424818333e-09</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0002440833195578307</v>
+        <v>1.717824771318988e-09</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0005180257139727473</v>
+        <v>1.51272683268644e-09</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.663021900341846e-05</v>
+        <v>1.68453329063567e-09</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.000161785603268072</v>
+        <v>4.287914745493282e-10</v>
       </c>
       <c r="AO17" t="n">
-        <v>4.75545457447879e-05</v>
+        <v>8.128622219771842e-10</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0003143370558973402</v>
+        <v>6.636355354139312e-11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0001357361325062811</v>
+        <v>3.738553910892506e-11</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0001323686738032848</v>
+        <v>2.639779228541528e-10</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0003382745489943773</v>
+        <v>1.04737751804862e-09</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.0004163339035585523</v>
+        <v>8.856760880249226e-10</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.001850805361755192</v>
+        <v>1.557784345962432e-09</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.317186878528446e-05</v>
+        <v>1.165657681490018e-09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0003933737461920828</v>
+        <v>2.452250069673312e-10</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0001270701177418232</v>
+        <v>1.125740278773435e-09</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0009859914425760508</v>
+        <v>1.018508610783897e-09</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0004804204218089581</v>
+        <v>7.898650622450987e-10</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0003022818418685347</v>
+        <v>2.7106109024011e-10</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.0006775622605346143</v>
+        <v>1.139261601723618e-11</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0002184918557759374</v>
+        <v>5.018098825360084e-09</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0006845276802778244</v>
+        <v>4.121808672152838e-09</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.000470369472168386</v>
+        <v>1.703795771135219e-09</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.690490070264786e-06</v>
+        <v>4.487687998988577e-12</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.000359762052539736</v>
+        <v>3.635886924868714e-09</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0005288240499794483</v>
+        <v>1.508806191097278e-09</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0002667436783667654</v>
+        <v>1.217677347842283e-10</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0002178059366997331</v>
+        <v>4.529757013926883e-09</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.0004607352311722934</v>
+        <v>5.432210681277638e-09</v>
       </c>
       <c r="BL17" t="n">
-        <v>4.027061368105933e-05</v>
+        <v>4.260732600069872e-10</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0004451006243471056</v>
+        <v>1.068460209197042e-09</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.0002057670790236443</v>
+        <v>1.170253893789663e-10</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.503691601101309e-05</v>
+        <v>1.295218599040027e-09</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.667926335358061e-05</v>
+        <v>3.449593943827267e-10</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0001033940789056942</v>
+        <v>1.419144357583946e-09</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0004019609477836639</v>
+        <v>1.197101306971149e-10</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.0002185769553761929</v>
+        <v>1.452348796782132e-09</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0002001971151912585</v>
+        <v>1.639242963591414e-09</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.000149001061799936</v>
+        <v>3.07156833301292e-09</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.001013225060887635</v>
+        <v>2.292330547604138e-09</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0002238885790575296</v>
+        <v>7.451516070844377e-10</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.0001865222293417901</v>
+        <v>8.604048029603462e-10</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0002044246793957427</v>
+        <v>9.269152806412606e-11</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0005086445016786456</v>
+        <v>1.000199256750989e-09</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0001122864341596141</v>
+        <v>8.322200706345484e-10</v>
       </c>
       <c r="CB17" t="n">
-        <v>6.418143311748281e-05</v>
+        <v>8.594660538818744e-10</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0004653797950595617</v>
+        <v>6.132375163225845e-10</v>
       </c>
       <c r="CD17" t="n">
-        <v>1.707663614070043e-05</v>
+        <v>3.262913550461377e-11</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.00043781942804344</v>
+        <v>2.527235087868007e-10</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0002557144034653902</v>
+        <v>2.5991744867504e-10</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0001521440863143653</v>
+        <v>2.163801637866669e-10</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0001739964645821601</v>
+        <v>2.100867951826402e-10</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.000231744023039937</v>
+        <v>4.433928779690177e-10</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.000202635710593313</v>
+        <v>2.345998742492306e-11</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0001234422670677304</v>
+        <v>2.136627819115944e-10</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0002393354661762714</v>
+        <v>5.039851314059263e-10</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0005687858210876584</v>
+        <v>2.829302347961971e-10</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0001510048459749669</v>
+        <v>7.269402857446039e-10</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0001173322962131351</v>
+        <v>1.223599443989087e-09</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0009491594973951578</v>
+        <v>4.792669594522181e-10</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0001728001661831513</v>
+        <v>3.689683003571531e-09</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0003274620103184134</v>
+        <v>1.079455066999024e-10</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.0006054230034351349</v>
+        <v>3.416702698544327e-09</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0005762487999163568</v>
+        <v>9.302061898530667e-10</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0001321404415648431</v>
+        <v>1.93804350345772e-09</v>
       </c>
       <c r="CV17" t="n">
-        <v>3.063718031626195e-05</v>
+        <v>4.452579971392367e-10</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0003894262772519141</v>
+        <v>3.161948480823185e-10</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0002382185048190877</v>
+        <v>3.469222131791128e-11</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.000313062162604183</v>
+        <v>2.876057725309522e-10</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0001894470333354548</v>
+        <v>8.616998781185714e-11</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0001821069454308599</v>
+        <v>2.142428873197488e-10</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0002083008730551228</v>
+        <v>1.45756975933331e-10</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0002793656894937158</v>
+        <v>1.603248228621013e-10</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.0001461643259972334</v>
+        <v>5.465409236293794e-10</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.0001522958918940276</v>
+        <v>8.476194190976116e-10</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0002213429543189704</v>
+        <v>2.155412071047635e-09</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.0001161384861916304</v>
+        <v>3.32825433879691e-09</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0007896851166151464</v>
+        <v>2.417081534922261e-10</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0005905930884182453</v>
+        <v>4.570124001457287e-10</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.0006126686348579824</v>
+        <v>2.793398845568618e-10</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.000258064828813076</v>
+        <v>2.443036328791948e-10</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0004960763035342097</v>
+        <v>1.646827896273351e-09</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0005068129976280034</v>
+        <v>9.730307670707816e-10</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.240287176391575e-05</v>
+        <v>1.464892984692767e-09</v>
       </c>
       <c r="DO17" t="n">
-        <v>7.424500654451549e-05</v>
+        <v>2.112794383890559e-09</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0002975109382532537</v>
+        <v>1.450001785308075e-10</v>
       </c>
       <c r="DQ17" t="n">
-        <v>3.891338928951882e-05</v>
+        <v>7.009256369761019e-11</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.000106747895188164</v>
+        <v>1.331740051568886e-09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0001906333927763626</v>
+        <v>1.270668570363398e-09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0003231667797081172</v>
+        <v>4.335802827881707e-10</v>
       </c>
       <c r="DU17" t="n">
-        <v>4.541871385299601e-05</v>
+        <v>2.911623164791877e-10</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.041845047846437e-06</v>
+        <v>7.520452038889403e-10</v>
       </c>
       <c r="DW17" t="n">
-        <v>7.259455742314458e-06</v>
+        <v>9.5758234675003e-10</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0002921777777373791</v>
+        <v>5.544656400680026e-10</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0002312680881004781</v>
+        <v>7.897393849987111e-10</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0003281287790741771</v>
+        <v>1.080405542808194e-09</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.000149851170135662</v>
+        <v>1.302170815620229e-09</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0001543551188660786</v>
+        <v>7.872039131662234e-11</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.854301419574767e-05</v>
+        <v>1.976980357198954e-09</v>
       </c>
       <c r="ED17" t="n">
-        <v>6.149060209281743e-05</v>
+        <v>1.764193013897852e-09</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.0002901730185840279</v>
+        <v>2.095981610494846e-09</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0001870728738140315</v>
+        <v>7.216204300775075e-10</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0005058028036728501</v>
+        <v>3.792841041239114e-11</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.0001277402916457504</v>
+        <v>3.571218321063441e-10</v>
       </c>
       <c r="EI17" t="n">
-        <v>8.530612831236795e-05</v>
+        <v>6.907149158186243e-11</v>
       </c>
       <c r="EJ17" t="n">
-        <v>8.826842531561852e-06</v>
+        <v>1.077547939765111e-09</v>
       </c>
       <c r="EK17" t="n">
-        <v>9.90509579423815e-05</v>
+        <v>1.429161677890534e-09</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0002605983172543347</v>
+        <v>1.043560127200749e-09</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0001059943315340206</v>
+        <v>2.899392184674277e-11</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0001381750626023859</v>
+        <v>8.779066917874445e-10</v>
       </c>
       <c r="EO17" t="n">
-        <v>7.965932309161872e-05</v>
+        <v>3.661548286792993e-10</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0001693708472885191</v>
+        <v>3.983285923325752e-12</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.000262957822997123</v>
+        <v>6.775257022084702e-10</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0003585810482036322</v>
+        <v>2.070992266567373e-10</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0003869709034916013</v>
+        <v>3.827691774649367e-10</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.0003347900055814534</v>
+        <v>9.619798291282677e-10</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0006096265278756618</v>
+        <v>7.548487945818749e-10</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0007073567830957472</v>
+        <v>1.61466517933917e-09</v>
       </c>
       <c r="EW17" t="n">
-        <v>6.676313932985067e-05</v>
+        <v>4.053851698770927e-10</v>
       </c>
       <c r="EX17" t="n">
-        <v>7.824660133337602e-05</v>
+        <v>3.342817411766674e-10</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.0003918937582056969</v>
+        <v>3.948020521615803e-10</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.0001951446174643934</v>
+        <v>1.348101352771636e-10</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0001275360118597746</v>
+        <v>3.613380705758118e-10</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0001704374881228432</v>
+        <v>1.948922551120447e-10</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.000183706171810627</v>
+        <v>5.585690798781684e-10</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.0003731484466698021</v>
+        <v>2.775762952822447e-10</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0002252680569654331</v>
+        <v>2.598820325605544e-10</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.000266029528575018</v>
+        <v>4.080865645406107e-10</v>
       </c>
       <c r="FG17" t="n">
-        <v>7.550418376922607e-05</v>
+        <v>2.374224150614168e-10</v>
       </c>
       <c r="FH17" t="n">
-        <v>9.998406312661245e-05</v>
+        <v>1.901848262209072e-10</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0003071638639084995</v>
+        <v>1.106628788605235e-09</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0004240829148329794</v>
+        <v>5.463833274710339e-10</v>
       </c>
       <c r="FK17" t="n">
-        <v>1.118220097851008e-05</v>
+        <v>2.403585663834917e-10</v>
       </c>
       <c r="FL17" t="n">
-        <v>5.717105523217469e-05</v>
+        <v>1.956302009276101e-09</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.0002257265732623637</v>
+        <v>4.824257660018816e-10</v>
       </c>
       <c r="FN17" t="n">
-        <v>6.079641752876341e-05</v>
+        <v>2.782817587476671e-10</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.000345197826391086</v>
+        <v>2.576377999830015e-09</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0003050802915822715</v>
+        <v>3.950859195356315e-09</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.000434919202234596</v>
+        <v>6.225787663183269e-10</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0002511414350010455</v>
+        <v>1.13027920356501e-10</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0002872783225029707</v>
+        <v>3.762307798638176e-09</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.000116741270176135</v>
+        <v>5.230837096803498e-09</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0004089983412995934</v>
+        <v>2.019049788470895e-10</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0004194100620225072</v>
+        <v>5.048952367303627e-10</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0003814916126430035</v>
+        <v>2.77741407650467e-09</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0001091506346710958</v>
+        <v>1.736822130560256e-09</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0006044681067578495</v>
+        <v>1.514693259707656e-09</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0002085015585180372</v>
+        <v>2.054626468961374e-09</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0001774251140886918</v>
+        <v>2.464641379873456e-09</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0002003666886594146</v>
+        <v>8.85141848705473e-10</v>
       </c>
       <c r="GC17" t="n">
-        <v>8.001503010746092e-05</v>
+        <v>9.614725682283165e-10</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0003490187809802592</v>
+        <v>5.827221483123424e-10</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.0008567256736569107</v>
+        <v>1.23270582630397e-09</v>
       </c>
       <c r="GF17" t="n">
-        <v>8.090276969596744e-05</v>
+        <v>1.787985315360174e-09</v>
       </c>
       <c r="GG17" t="n">
-        <v>1.013339351629838e-05</v>
+        <v>1.038917951667884e-09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.809473244269611e-06</v>
+        <v>7.666378110116057e-08</v>
       </c>
       <c r="B18" t="n">
-        <v>1.658105065871496e-05</v>
+        <v>1.142393131203789e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605075112820487e-06</v>
+        <v>6.666982699243817e-08</v>
       </c>
       <c r="D18" t="n">
-        <v>1.32879322336521e-05</v>
+        <v>9.207350615270116e-08</v>
       </c>
       <c r="E18" t="n">
-        <v>6.22611514700111e-06</v>
+        <v>1.335000234803374e-07</v>
       </c>
       <c r="F18" t="n">
-        <v>2.223194542239071e-06</v>
+        <v>1.286963424718124e-07</v>
       </c>
       <c r="G18" t="n">
-        <v>8.398512818530435e-07</v>
+        <v>1.311272512793948e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>2.130318989657098e-06</v>
+        <v>2.169415154185117e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>1.094757521968859e-06</v>
+        <v>1.133433187305855e-07</v>
       </c>
       <c r="J18" t="n">
-        <v>3.828065473499009e-06</v>
+        <v>5.397252778038819e-08</v>
       </c>
       <c r="K18" t="n">
-        <v>1.241134486917872e-05</v>
+        <v>7.538301360909827e-08</v>
       </c>
       <c r="L18" t="n">
-        <v>1.159369844572211e-06</v>
+        <v>1.491211065740572e-08</v>
       </c>
       <c r="M18" t="n">
-        <v>1.002973112917971e-05</v>
+        <v>2.057678614164615e-07</v>
       </c>
       <c r="N18" t="n">
-        <v>8.280100701085757e-06</v>
+        <v>2.513957895189378e-07</v>
       </c>
       <c r="O18" t="n">
-        <v>8.352429176738951e-06</v>
+        <v>1.423844651071704e-07</v>
       </c>
       <c r="P18" t="n">
-        <v>1.777254055923549e-06</v>
+        <v>1.491587937607619e-07</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.003791905735852e-06</v>
+        <v>1.973313032976876e-07</v>
       </c>
       <c r="R18" t="n">
-        <v>6.815682809246937e-07</v>
+        <v>7.097307985759471e-08</v>
       </c>
       <c r="S18" t="n">
-        <v>6.895140813867329e-08</v>
+        <v>1.843956454194995e-08</v>
       </c>
       <c r="T18" t="n">
-        <v>3.878578809235478e-06</v>
+        <v>3.11217362991556e-08</v>
       </c>
       <c r="U18" t="n">
-        <v>4.591151423483097e-07</v>
+        <v>6.276657416037779e-08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.505763520981418e-06</v>
+        <v>4.70584726741663e-09</v>
       </c>
       <c r="W18" t="n">
-        <v>2.640689444888267e-06</v>
+        <v>1.275452987670178e-08</v>
       </c>
       <c r="X18" t="n">
-        <v>2.468265392963076e-06</v>
+        <v>1.828394502467745e-08</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.219713562430115e-06</v>
+        <v>1.332370325179966e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.567921913192549e-06</v>
+        <v>4.874821968314791e-08</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.478800181255792e-06</v>
+        <v>1.346854716643975e-08</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.984489467256935e-07</v>
+        <v>4.153099553150241e-08</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.431965185678564e-06</v>
+        <v>8.077962831976038e-08</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.809280774978106e-06</v>
+        <v>4.737391634535015e-08</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.185483142762678e-06</v>
+        <v>3.38214931616676e-08</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.133084083448921e-06</v>
+        <v>7.312953442806247e-08</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.486973340244731e-07</v>
+        <v>1.107517135778835e-07</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.22671042138245e-06</v>
+        <v>3.254137403985169e-09</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.360205364013382e-07</v>
+        <v>1.523067396647093e-07</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.450937503477689e-07</v>
+        <v>4.317388402341749e-08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.443326593493111e-06</v>
+        <v>2.199340620734347e-08</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.041759671556065e-06</v>
+        <v>1.205190613973173e-09</v>
       </c>
       <c r="AM18" t="n">
-        <v>5.144946726431954e-07</v>
+        <v>7.529398260430753e-08</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.061771740751283e-06</v>
+        <v>2.361327577915517e-09</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.21239315578714e-06</v>
+        <v>5.973059558073146e-08</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.200173045390329e-07</v>
+        <v>1.214316203146382e-08</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.775652208380052e-06</v>
+        <v>1.267436999796701e-08</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.75310468270618e-07</v>
+        <v>5.439726180611615e-08</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.284649670196814e-06</v>
+        <v>5.127210211952615e-09</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.178708998850198e-06</v>
+        <v>4.252233765100755e-08</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.331370276602684e-05</v>
+        <v>9.398021916240396e-08</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.574056907178601e-06</v>
+        <v>7.300906190721435e-08</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.190767074556788e-06</v>
+        <v>4.131797126660786e-08</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.370091749526182e-07</v>
+        <v>2.608620093269565e-07</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.698324751941982e-07</v>
+        <v>2.224664115146879e-07</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.269332182753715e-07</v>
+        <v>5.142092618370953e-08</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.538101165962871e-06</v>
+        <v>4.602244985107973e-08</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.294667506765109e-07</v>
+        <v>8.630051340219325e-09</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.504449968109839e-07</v>
+        <v>1.558508699872618e-08</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.340929879414034e-07</v>
+        <v>1.499589217246466e-07</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.515310360555304e-06</v>
+        <v>2.675900390158858e-09</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.645339691298432e-06</v>
+        <v>9.812899293137889e-08</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.591756118723424e-06</v>
+        <v>8.939556295217699e-08</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.827209527822561e-06</v>
+        <v>1.121560373462671e-07</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.662858153395064e-06</v>
+        <v>1.136353677821944e-09</v>
       </c>
       <c r="BJ18" t="n">
-        <v>3.237367081965203e-06</v>
+        <v>1.530198545651729e-07</v>
       </c>
       <c r="BK18" t="n">
-        <v>2.02917163960592e-07</v>
+        <v>1.128953996953896e-07</v>
       </c>
       <c r="BL18" t="n">
-        <v>2.653547653608257e-06</v>
+        <v>3.774696111236153e-08</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.667727353080409e-06</v>
+        <v>1.40971422979419e-07</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.254913735872833e-06</v>
+        <v>3.354147537493191e-08</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.914081167342374e-06</v>
+        <v>5.713424400255462e-08</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.27467512054136e-06</v>
+        <v>6.767412230601622e-08</v>
       </c>
       <c r="BQ18" t="n">
-        <v>2.169065965063055e-06</v>
+        <v>3.681805527122606e-09</v>
       </c>
       <c r="BR18" t="n">
-        <v>7.402444452964119e-07</v>
+        <v>5.31133359515934e-08</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.984867478517117e-06</v>
+        <v>8.477314139554437e-08</v>
       </c>
       <c r="BT18" t="n">
-        <v>2.047148427664069e-06</v>
+        <v>9.939686407278714e-09</v>
       </c>
       <c r="BU18" t="n">
-        <v>7.451351393683581e-07</v>
+        <v>1.143999739383617e-08</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.710606157867005e-06</v>
+        <v>3.516134938763571e-08</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.459396000631386e-06</v>
+        <v>7.791922485012037e-08</v>
       </c>
       <c r="BX18" t="n">
-        <v>1.465961418034567e-06</v>
+        <v>3.367996015413155e-08</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.474168129789177e-07</v>
+        <v>4.429355016100089e-08</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.282732682739152e-06</v>
+        <v>7.478642061187202e-08</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.100333287875401e-06</v>
+        <v>5.113400192158224e-08</v>
       </c>
       <c r="CB18" t="n">
-        <v>1.165748471976258e-06</v>
+        <v>5.392017143890371e-08</v>
       </c>
       <c r="CC18" t="n">
-        <v>1.697987158877368e-06</v>
+        <v>1.881521072277792e-08</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.699668246146757e-07</v>
+        <v>1.695892670738885e-08</v>
       </c>
       <c r="CE18" t="n">
-        <v>2.706833356569405e-06</v>
+        <v>2.223516126775849e-08</v>
       </c>
       <c r="CF18" t="n">
-        <v>1.99351802621095e-06</v>
+        <v>2.672535526215825e-09</v>
       </c>
       <c r="CG18" t="n">
-        <v>1.016632836581266e-06</v>
+        <v>4.258269470369669e-08</v>
       </c>
       <c r="CH18" t="n">
-        <v>3.712572151925997e-07</v>
+        <v>5.270984360095099e-08</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.194514766211796e-06</v>
+        <v>5.013703230360989e-08</v>
       </c>
       <c r="CJ18" t="n">
-        <v>4.662415449274704e-07</v>
+        <v>4.870466696615949e-09</v>
       </c>
       <c r="CK18" t="n">
-        <v>5.907945705985185e-07</v>
+        <v>2.529981557586325e-09</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.726179561956087e-06</v>
+        <v>2.685296074389498e-08</v>
       </c>
       <c r="CM18" t="n">
-        <v>3.896803718816955e-06</v>
+        <v>6.747257685901786e-08</v>
       </c>
       <c r="CN18" t="n">
-        <v>8.374228741558909e-07</v>
+        <v>1.467820283096444e-07</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.735265414026799e-06</v>
+        <v>1.704007814851138e-07</v>
       </c>
       <c r="CP18" t="n">
-        <v>5.204315129958559e-06</v>
+        <v>7.928220924213747e-08</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.590785354390391e-06</v>
+        <v>1.460927556706793e-08</v>
       </c>
       <c r="CR18" t="n">
-        <v>5.84658437219332e-07</v>
+        <v>2.108678209822301e-08</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.449613359407522e-06</v>
+        <v>7.756336373176964e-08</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.641771459366282e-07</v>
+        <v>2.913237118207235e-08</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.19770004403108e-06</v>
+        <v>4.369183059793613e-08</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.620220047016119e-07</v>
+        <v>1.143700689709704e-08</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.274733787999139e-06</v>
+        <v>1.376211855586007e-08</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.821907858357008e-06</v>
+        <v>3.24557536401926e-09</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.093994680762989e-06</v>
+        <v>6.005127062280735e-08</v>
       </c>
       <c r="CZ18" t="n">
-        <v>1.07400137494551e-06</v>
+        <v>5.187101947967676e-08</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.511067694082158e-06</v>
+        <v>5.420010040779744e-08</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.092303591576638e-06</v>
+        <v>3.166989448466495e-10</v>
       </c>
       <c r="DC18" t="n">
-        <v>7.208464580799046e-07</v>
+        <v>4.274438580864626e-09</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.220538251800463e-06</v>
+        <v>1.916687075720347e-08</v>
       </c>
       <c r="DE18" t="n">
-        <v>3.031518417628831e-06</v>
+        <v>2.352812344952326e-08</v>
       </c>
       <c r="DF18" t="n">
-        <v>3.221072120140889e-07</v>
+        <v>5.848043826972571e-09</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.860785793425748e-06</v>
+        <v>3.576339224764524e-08</v>
       </c>
       <c r="DH18" t="n">
-        <v>7.570969501102809e-06</v>
+        <v>4.980568490964288e-08</v>
       </c>
       <c r="DI18" t="n">
-        <v>2.432720521028386e-06</v>
+        <v>1.863024756687537e-08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>4.838684617425315e-07</v>
+        <v>1.301893064464821e-07</v>
       </c>
       <c r="DK18" t="n">
-        <v>8.364089580936707e-07</v>
+        <v>5.858970197891722e-09</v>
       </c>
       <c r="DL18" t="n">
-        <v>2.800397624014295e-06</v>
+        <v>4.649939810974502e-08</v>
       </c>
       <c r="DM18" t="n">
-        <v>9.829374221226317e-07</v>
+        <v>4.802363662292919e-08</v>
       </c>
       <c r="DN18" t="n">
-        <v>4.081823590240674e-07</v>
+        <v>4.201914904911064e-08</v>
       </c>
       <c r="DO18" t="n">
-        <v>5.601468728855252e-07</v>
+        <v>3.242634250000265e-08</v>
       </c>
       <c r="DP18" t="n">
-        <v>2.538873559387866e-06</v>
+        <v>3.587302899177303e-08</v>
       </c>
       <c r="DQ18" t="n">
-        <v>8.181287398656423e-07</v>
+        <v>1.201062893585458e-08</v>
       </c>
       <c r="DR18" t="n">
-        <v>5.066428343525331e-07</v>
+        <v>1.837563345929993e-08</v>
       </c>
       <c r="DS18" t="n">
-        <v>4.894052381132497e-07</v>
+        <v>1.904609980840632e-08</v>
       </c>
       <c r="DT18" t="n">
-        <v>4.803117690244108e-07</v>
+        <v>2.795776765651681e-08</v>
       </c>
       <c r="DU18" t="n">
-        <v>9.217226306645898e-07</v>
+        <v>9.967153857814992e-08</v>
       </c>
       <c r="DV18" t="n">
-        <v>2.551777242842945e-06</v>
+        <v>2.757466788239071e-08</v>
       </c>
       <c r="DW18" t="n">
-        <v>3.246645974286366e-07</v>
+        <v>7.45004236080149e-09</v>
       </c>
       <c r="DX18" t="n">
-        <v>3.581598321034107e-06</v>
+        <v>5.454862517240144e-08</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.698319687828189e-06</v>
+        <v>1.733764420919215e-08</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.470144349648763e-08</v>
+        <v>3.711538099082645e-08</v>
       </c>
       <c r="EA18" t="n">
-        <v>1.202561065838381e-06</v>
+        <v>2.042419389169936e-08</v>
       </c>
       <c r="EB18" t="n">
-        <v>3.359319180162856e-06</v>
+        <v>5.464642782726514e-08</v>
       </c>
       <c r="EC18" t="n">
-        <v>7.601746574437129e-07</v>
+        <v>3.939147319442782e-08</v>
       </c>
       <c r="ED18" t="n">
-        <v>4.90560807975271e-07</v>
+        <v>8.908649107297606e-08</v>
       </c>
       <c r="EE18" t="n">
-        <v>6.324876267171931e-07</v>
+        <v>4.074786374985706e-08</v>
       </c>
       <c r="EF18" t="n">
-        <v>1.300747840105032e-06</v>
+        <v>1.78909509429559e-09</v>
       </c>
       <c r="EG18" t="n">
-        <v>1.682904212430003e-06</v>
+        <v>2.728243941874098e-08</v>
       </c>
       <c r="EH18" t="n">
-        <v>9.904517810355173e-07</v>
+        <v>2.249021413547325e-09</v>
       </c>
       <c r="EI18" t="n">
-        <v>1.479862589803815e-06</v>
+        <v>6.334451541079034e-08</v>
       </c>
       <c r="EJ18" t="n">
-        <v>2.116036284860456e-06</v>
+        <v>1.693055118323628e-08</v>
       </c>
       <c r="EK18" t="n">
-        <v>1.07140670024819e-06</v>
+        <v>8.43279650553086e-08</v>
       </c>
       <c r="EL18" t="n">
-        <v>1.600597784090496e-06</v>
+        <v>1.413357697543915e-08</v>
       </c>
       <c r="EM18" t="n">
-        <v>1.282399011870439e-06</v>
+        <v>3.010802984704242e-08</v>
       </c>
       <c r="EN18" t="n">
-        <v>5.887015959160635e-07</v>
+        <v>1.480539246756507e-08</v>
       </c>
       <c r="EO18" t="n">
-        <v>2.981901161547285e-07</v>
+        <v>3.371987133959919e-08</v>
       </c>
       <c r="EP18" t="n">
-        <v>9.577230457580299e-07</v>
+        <v>3.970955475551818e-08</v>
       </c>
       <c r="EQ18" t="n">
-        <v>2.396980107732816e-06</v>
+        <v>2.341771043745666e-08</v>
       </c>
       <c r="ER18" t="n">
-        <v>8.789331218395091e-08</v>
+        <v>2.85736856397989e-08</v>
       </c>
       <c r="ES18" t="n">
-        <v>1.868050617304107e-06</v>
+        <v>2.787458086572769e-08</v>
       </c>
       <c r="ET18" t="n">
-        <v>3.958626564326551e-07</v>
+        <v>7.817769542839414e-09</v>
       </c>
       <c r="EU18" t="n">
-        <v>1.253853383786918e-06</v>
+        <v>1.851905295779943e-08</v>
       </c>
       <c r="EV18" t="n">
-        <v>3.106696567556355e-06</v>
+        <v>7.268605273225148e-09</v>
       </c>
       <c r="EW18" t="n">
-        <v>1.211161702485697e-06</v>
+        <v>3.322644914760531e-08</v>
       </c>
       <c r="EX18" t="n">
-        <v>4.331501770593604e-07</v>
+        <v>1.608668043218131e-08</v>
       </c>
       <c r="EY18" t="n">
-        <v>2.164047828046023e-06</v>
+        <v>4.290904342951762e-08</v>
       </c>
       <c r="EZ18" t="n">
-        <v>1.599482970959798e-06</v>
+        <v>4.358436278550926e-09</v>
       </c>
       <c r="FA18" t="n">
-        <v>1.294003823204548e-06</v>
+        <v>5.068621433679255e-08</v>
       </c>
       <c r="FB18" t="n">
-        <v>5.680760750692571e-09</v>
+        <v>4.829842126241601e-08</v>
       </c>
       <c r="FC18" t="n">
-        <v>1.438951358068152e-06</v>
+        <v>5.794620605570344e-08</v>
       </c>
       <c r="FD18" t="n">
-        <v>8.006699658835714e-07</v>
+        <v>4.497165306815987e-09</v>
       </c>
       <c r="FE18" t="n">
-        <v>2.691105294161389e-07</v>
+        <v>8.498227010989012e-09</v>
       </c>
       <c r="FF18" t="n">
-        <v>1.930848384290584e-06</v>
+        <v>6.303824573450356e-09</v>
       </c>
       <c r="FG18" t="n">
-        <v>1.300948497373611e-06</v>
+        <v>5.824424675893169e-08</v>
       </c>
       <c r="FH18" t="n">
-        <v>1.608064394531539e-06</v>
+        <v>2.038168034346199e-08</v>
       </c>
       <c r="FI18" t="n">
-        <v>4.365230324765434e-06</v>
+        <v>3.523457792198315e-08</v>
       </c>
       <c r="FJ18" t="n">
-        <v>2.795230329866172e-06</v>
+        <v>1.030277019253845e-08</v>
       </c>
       <c r="FK18" t="n">
-        <v>7.644734409950615e-07</v>
+        <v>9.620501373319712e-08</v>
       </c>
       <c r="FL18" t="n">
-        <v>2.412725450540165e-07</v>
+        <v>3.053911257211439e-08</v>
       </c>
       <c r="FM18" t="n">
-        <v>9.829577720665839e-07</v>
+        <v>3.812516879975192e-08</v>
       </c>
       <c r="FN18" t="n">
-        <v>2.222478315161425e-06</v>
+        <v>7.333856899549573e-08</v>
       </c>
       <c r="FO18" t="n">
-        <v>1.936860599016654e-06</v>
+        <v>1.10916204221212e-07</v>
       </c>
       <c r="FP18" t="n">
-        <v>7.505830694753968e-07</v>
+        <v>8.43411029904928e-09</v>
       </c>
       <c r="FQ18" t="n">
-        <v>2.772993411781499e-06</v>
+        <v>1.121446047136487e-08</v>
       </c>
       <c r="FR18" t="n">
-        <v>1.430886982234369e-07</v>
+        <v>1.164857863500401e-07</v>
       </c>
       <c r="FS18" t="n">
-        <v>1.464575802856416e-07</v>
+        <v>4.967944988720774e-08</v>
       </c>
       <c r="FT18" t="n">
-        <v>3.865409325953806e-06</v>
+        <v>2.583567138003673e-08</v>
       </c>
       <c r="FU18" t="n">
-        <v>1.085606982087484e-06</v>
+        <v>2.533671228377443e-08</v>
       </c>
       <c r="FV18" t="n">
-        <v>2.746762220340315e-06</v>
+        <v>1.227571431172692e-07</v>
       </c>
       <c r="FW18" t="n">
-        <v>1.084993527911138e-06</v>
+        <v>1.650891476856486e-07</v>
       </c>
       <c r="FX18" t="n">
-        <v>2.35415541283146e-06</v>
+        <v>5.950145265387619e-08</v>
       </c>
       <c r="FY18" t="n">
-        <v>4.188178536423948e-06</v>
+        <v>2.006828481171397e-08</v>
       </c>
       <c r="FZ18" t="n">
-        <v>2.135103841283126e-06</v>
+        <v>7.2347930313299e-08</v>
       </c>
       <c r="GA18" t="n">
-        <v>9.346578622171364e-08</v>
+        <v>1.069696651256891e-07</v>
       </c>
       <c r="GB18" t="n">
-        <v>3.643971808742208e-07</v>
+        <v>7.64851293411084e-09</v>
       </c>
       <c r="GC18" t="n">
-        <v>5.334486559149809e-06</v>
+        <v>1.134008016379084e-07</v>
       </c>
       <c r="GD18" t="n">
-        <v>2.460961695760489e-06</v>
+        <v>1.268072082893923e-07</v>
       </c>
       <c r="GE18" t="n">
-        <v>5.809892627439694e-06</v>
+        <v>3.212984722722467e-08</v>
       </c>
       <c r="GF18" t="n">
-        <v>5.639505502585962e-07</v>
+        <v>2.953648881032223e-09</v>
       </c>
       <c r="GG18" t="n">
-        <v>2.144426616723649e-06</v>
+        <v>1.667858740006523e-09</v>
       </c>
     </row>
   </sheetData>
